--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>id</t>
   </si>
@@ -186,6 +186,37 @@
 遠くで 別の宇宙服が同じ料理を受け取っている
 地上はもうないのに、この街だけが昭和の匂いを守りながら
 宇宙で夕食を続けている</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <t>ガスマスク,真空管装置,人機融合</t>
+  </si>
+  <si>
+    <t>ガラスドームの呼吸</t>
+  </si>
+  <si>
+    <t>26.03.03</t>
+  </si>
+  <si>
+    <t>高層ビルの光がにじむ夜
+ガラスドームの中で私はホースを握り直した
+このアナログPCと向き合って何年になるだろう
+デジタル全盛の街であえて真空管とダイヤルにこだわり
+ガスケーブルと人体を接続する実験を続けてきた
+効率の悪い古い機械
+だがこいつは嘘をつかない
+数字ではなく振動で応える
+ブウウウン
+計器の針がカチリと震える
+若い頃は無謀だと言われた
+それでもここまで辿り着いた
+この密閉空間でコンピューターと人間を結び
+新しい生命体を起こす
+さあ動いてくれ
+奴らが来る前にこの都市の呼吸を
+こちら側へ奪い取るんだ</t>
   </si>
 </sst>
 </file>
@@ -752,11 +783,21 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -217,6 +217,33 @@
 さあ動いてくれ
 奴らが来る前にこの都市の呼吸を
 こちら側へ奪い取るんだ</t>
+  </si>
+  <si>
+    <t>0009</t>
+  </si>
+  <si>
+    <t>奇妙な養殖場,#進化の儀式,念仏</t>
+  </si>
+  <si>
+    <t>進化の供物</t>
+  </si>
+  <si>
+    <t>26.03.05</t>
+  </si>
+  <si>
+    <t>よしよし
+今日もよく集まってるな。
+水の底からぬうっと顔を出すあの影を見るたび
+胸の奥が静かに震える
+ナムナム
+念仏の効果か
+ここ数年で知能が確実に上がってきている
+目が合うとわかるんだ
+あいつらはこちらを理解し始めている
+村のみんなのために
+料理にするのが惜しいが、仕方ない。
+食べることで我々はまた
+少しだけ近づけるのだから。</t>
   </si>
 </sst>
 </file>
@@ -820,11 +847,21 @@
       <c r="Y9" s="3"/>
     </row>
     <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="A10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -244,6 +244,46 @@
 料理にするのが惜しいが、仕方ない。
 食べることで我々はまた
 少しだけ近づけるのだから。</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>異界事務所,契約,ゴースト</t>
+  </si>
+  <si>
+    <t>棘の役人</t>
+  </si>
+  <si>
+    <t>26.03.07</t>
+  </si>
+  <si>
+    <t>カリカリ
+ああ今日も一件妙な契約が増えた
+ここで仕事を始めてもうどのくらい経つだろう
+誰もこの中に俺のデスクがあるなんて思っていない
+外から見ればただの棘だらけのサボテンだ
+だが中ではこうして紙の音が続いている
+カリカリ
+空間は歪み
+時間はゆっくり淀み、時代はそのたび形を変える
+俺があの世にいたのは
+いつ頃だったのだろう
+まあ そんなことはどうでもいい
+周りに執着せず好きなことだけに没頭する
+それだけで時間はちゃんと流れてくれる
+理解する人？
+はは、そんなものはいらない
+俺にはこの紙とこのペンがあれば十分だ
+さあ今日の要件を聞こうか
+君が求めるものは何だい？
+復讐か
+再生か
+ゆっくりでいい
+君のタイミングで少しずつ語ってくれ
+トロリ
+今日もまた、この世界のどこかで異常な出来事が
+断面から静かに垂れ落ちている</t>
   </si>
 </sst>
 </file>
@@ -884,11 +924,21 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="A11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -284,6 +284,48 @@
 トロリ
 今日もまた、この世界のどこかで異常な出来事が
 断面から静かに垂れ落ちている</t>
+  </si>
+  <si>
+    <t>0011</t>
+  </si>
+  <si>
+    <t>火星オフィス,巨大蜘蛛,トマトジュース</t>
+  </si>
+  <si>
+    <t>前任者たちの残した席</t>
+  </si>
+  <si>
+    <t>26.03.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ブウウン
+よし今日も仕事だ
+火星に来てからもうどれくらい経っただろう
+最初はこの赤い大地も、
+天井のレールにぶら下がるあの巨大な監視装置も、どうにも落ち着かなかった
+だが人間というのは不思議なもので
+毎日こうして机に向かっていると、だんだん慣れてくる
+グククク
+背後であいつの脚がゆっくり動く
+どうやら今日も機嫌は悪くないらしい
+前任者たちは、まあ見ての通りだ
+耐えきれなかったんだろう。
+環境か
+孤独か
+それともあいつの視線か
+カサカサ
+天井のレールの上で
+蜘蛛がまた少し位置を変える
+来訪者の船も今日もはいくつか飛んでいる
+ここはどうやら見世物としても人気らしい
+食事？
+ああトマトジュースだけだよ
+足元の赤い液体？
+違う違うあれもトマトジュースだ
+君変なこと言うね
+さてと
+上司にメールして今日の仕事も終わりっと
+</t>
   </si>
 </sst>
 </file>
@@ -961,11 +1003,21 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="A12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -316,15 +316,15 @@
 カサカサ
 天井のレールの上で
 蜘蛛がまた少し位置を変える
-来訪者の船も今日もはいくつか飛んでいる
+来訪者の船も今日もいくつか飛んでいる
 ここはどうやら見世物としても人気らしい
 食事？
 ああトマトジュースだけだよ
 足元の赤い液体？
 違う違うあれもトマトジュースだ
 君変なこと言うね
-さてと
-上司にメールして今日の仕事も終わりっと
+さてと、
+上司にメールして今日の仕事も終わりにするか
 </t>
   </si>
 </sst>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>id</t>
   </si>
@@ -298,34 +298,80 @@
     <t>26.03.08</t>
   </si>
   <si>
-    <t xml:space="preserve">ブウウン
-よし今日も仕事だ
-火星に来てからもうどれくらい経っただろう
-最初はこの赤い大地も、
-天井のレールにぶら下がるあの巨大な監視装置も、どうにも落ち着かなかった
-だが人間というのは不思議なもので
-毎日こうして机に向かっていると、だんだん慣れてくる
-グククク
+    <t>火星に来てからもうどれくらい経っただろう
+赤い大地も
+天井にぶら下がる巨大な監視装置も
+毎日こうして机に向かっていると
+だんだん慣れてくる
+グオングオン
 背後であいつの脚がゆっくり動く
 どうやら今日も機嫌は悪くないらしい
-前任者たちは、まあ見ての通りだ
-耐えきれなかったんだろう。
+前任者たち？
+まあ見ての通りだ、
+耐えきれなかったんだろう
 環境か
 孤独か
 それともあいつの視線か
-カサカサ
-天井のレールの上で
-蜘蛛がまた少し位置を変える
-来訪者の船も今日もいくつか飛んでいる
-ここはどうやら見世物としても人気らしい
+来訪者の船が今日もいくつか飛んでいる
+どうやら見世物としても人気らしい
 食事？
-ああトマトジュースだけだよ
+トマトジュースだけだ
 足元の赤い液体？
-違う違うあれもトマトジュースだ
+あれもトマトジュースだ
 君変なこと言うね
-さてと、
-上司にメールして今日の仕事も終わりにするか
-</t>
+さて上司にメールして今日の仕事も終わりだ</t>
+  </si>
+  <si>
+    <t>0012</t>
+  </si>
+  <si>
+    <t>バイオパンク,森の研究所,自給自足</t>
+  </si>
+  <si>
+    <t>根と機械の研究所</t>
+  </si>
+  <si>
+    <t>文明が終わりかけたのは
+いつだったろう
+もう正確には思い出せない
+あの時
+直感で森へ逃げ込んだ
+今思えば正解だった
+そのあと都市は崩れた
+ネットワークも国家も
+静かに消えていった
+人間というのは
+なんと欲深い生き物だろう
+結局 自分たちで壊した
+今の俺の巣はここだ
+森の奥に埋めた
+このカプセル
+見てくれ
+カプセルの下から
+木の根が伸びている
+ぬるぬる
+この根から
+養分 水分 無機物質を取り出す
+森は巨大な装置だ
+その栄養でエビを養殖し
+野菜を育てる
+電気も問題ない
+このPUPAシステム
+当時最高の技術だった
+森の循環を読み取り
+必要な電力も
+自動で作ってくれる
+シュオンシュオン
+あれ以来人間には
+一度も会っていない
+世界がどうなったのか
+正直あまり興味もない
+どこかで誰かが
+静かに生き延びているならそれでいい
+さて
+今日はエビの出来がいい
+少し収穫するか
+森は今日も静かに呼吸している</t>
   </si>
 </sst>
 </file>
@@ -1040,11 +1086,21 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="4"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="A13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
   <si>
     <t>id</t>
   </si>
@@ -373,6 +373,42 @@
 少し収穫するか
 森は今日も静かに呼吸している</t>
   </si>
+  <si>
+    <t>0013</t>
+  </si>
+  <si>
+    <t>月面基地,発光クラゲ,宇宙養殖</t>
+  </si>
+  <si>
+    <t>月エビの夜</t>
+  </si>
+  <si>
+    <t>月面に来てどれだけ経ったろう
+ここには何もない
+月の地下から水を汲み上げて
+なんとか暮らしている
+友達？
+そんなものはいないさ
+まあ強いて言うならお前だな
+今日はずいぶん
+ぼうっと光ってやがる
+なんだ？
+そんな寂しそうに俺を見るなよ
+このエビ食えるか？月海老。
+なかなかうまいんだ
+ジュウウ
+まあ無理するな。
+これから先も長い
+しっかり付き合ってくれ
+俺がここに派遣されて
+もうどれくらい経つのか
+地球の連中は俺のことを覚えているかね
+通信はこの古いアナログ回線だけ
+ブウウン
+今日の夜も不気味だ
+月の静けさが俺の孤独を
+少しずつ深くしていく</t>
+  </si>
 </sst>
 </file>
 
@@ -1123,11 +1159,21 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="A14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
   <si>
     <t>id</t>
   </si>
@@ -84,6 +84,27 @@
   </si>
   <si>
     <t>26.02.28</t>
+  </si>
+  <si>
+    <t>引っ越してもう二年か。
+結構時間が経ったもんだ。
+最初は少し違和感もあったが
+住んでみると意外と快適だ。
+今の時代、どこに住んでいても仕事はできる。
+距離なんてほとんど関係ない。
+この住宅、時々奥の方から
+ググーググーって低い音がするんだ。
+気になって上司に電話したら
+「ああ、そんなもんだ。気にするな」って言われた。
+まあ確かに、生活には特に支障はない。
+ただもう一つ少し気になることがある。
+ムチュムチュ
+朝何かを咀嚼するような音がするんだ。
+食事はこの森で採れた木の実と
+昆虫のミックスサラダ。
+栄養があって悪くない。
+さあいつも通りメールを打とう。
+今日も世界が平和でありますように。</t>
   </si>
   <si>
     <t>0005</t>
@@ -839,7 +860,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -864,19 +885,19 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -901,19 +922,19 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -938,19 +959,19 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -975,19 +996,19 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -1012,19 +1033,19 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -1049,19 +1070,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -1086,19 +1107,19 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -1123,19 +1144,19 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -1160,19 +1181,19 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -100,7 +100,8 @@
 ただもう一つ少し気になることがある。
 ムチュムチュ
 朝何かを咀嚼するような音がするんだ。
-食事はこの森で採れた木の実と
+あの後は一体なんなんだろうか。
+俺の食事はこの森で採れた木の実と
 昆虫のミックスサラダ。
 栄養があって悪くない。
 さあいつも通りメールを打とう。

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -97,15 +97,15 @@
 気になって上司に電話したら
 「ああ、そんなもんだ。気にするな」って言われた。
 まあ確かに、生活には特に支障はない。
-ただもう一つ少し気になることがある。
+ただもう一つ少し気になることがある
 ムチュムチュ
-朝何かを咀嚼するような音がするんだ。
-あの後は一体なんなんだろうか。
+朝何かを咀嚼するような音がするんだ
+あれは一体なんなんだろう。
 俺の食事はこの森で採れた木の実と
-昆虫のミックスサラダ。
+昆虫のミックスサラダ
 栄養があって悪くない。
-さあいつも通りメールを打とう。
-今日も世界が平和でありますように。</t>
+さあいつも通り上司へメールだ
+今日も世界が平和でありますように</t>
   </si>
   <si>
     <t>0005</t>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="69">
   <si>
     <t>id</t>
   </si>
@@ -431,6 +431,42 @@
 月の静けさが俺の孤独を
 少しずつ深くしていく</t>
   </si>
+  <si>
+    <t>0014</t>
+  </si>
+  <si>
+    <t>時間の交差点,巨大昆虫,時間旅行</t>
+  </si>
+  <si>
+    <t>歴史が渡る朝</t>
+  </si>
+  <si>
+    <t>26.03.11</t>
+  </si>
+  <si>
+    <t>この横断歩道はただの道路ではない
+ここでは異なる時代の人間が
+同じ時間に歩いている
+古代の兵士
+近代の紳士
+昭和の会社員
+彼らは自分がどこから来たのかを知らない
+ザッザッ
+ただ信号が変われば歩き出す
+空では巨大な昆虫が
+静かに旋回している
+ブゥゥン
+人々はそれを気にも留めない
+彼らは観察されていることを
+知らないからだ
+ただ一人
+横断歩道の中央で傘をさした男だけが
+歩みを少し遅くする
+彼だけは知っている
+この道が
+人類の時間を渡らせるための
+交差点だということを</t>
+  </si>
 </sst>
 </file>
 
@@ -1218,11 +1254,21 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="A15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
   <si>
     <t>id</t>
   </si>
@@ -467,6 +467,42 @@
 人類の時間を渡らせるための
 交差点だということを</t>
   </si>
+  <si>
+    <t>0015</t>
+  </si>
+  <si>
+    <t>脳の文明,思考カプセル,脳AI</t>
+  </si>
+  <si>
+    <t>思考カプセル工場</t>
+  </si>
+  <si>
+    <t>26.03.15</t>
+  </si>
+  <si>
+    <t>当初想定していたスケジュールとはギャップがある
+だが問題はない
+未来はおおむね設計図どおりに進み始めている
+ビクリビクリ
+脆弱な器だったからか
+肉体はとうに失われた
+だが脳だけはこの世界のネットワークに接続され
+静かに人間たちを動かしている
+彼らは気づいていない
+今ようやく人類のテクノロジーが
+私の時代に追いつき始めた
+キュウウン、カチ
+私のアイデアはカプセルに封入され
+AIと結合しロボティクスと融合する
+新しい人類はそこから作られる
+理想の世界か？
+いや特にない
+私はただ破壊と創造を繰り返し
+その中で生まれるアノニマスを観察する
+さて、これは何回目の世界だったかな
+まあいい
+世界は今日も仕事で回っているのだから。</t>
+  </si>
 </sst>
 </file>
 
@@ -1291,11 +1327,21 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="A16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="79">
   <si>
     <t>id</t>
   </si>
@@ -503,6 +503,46 @@
 まあいい
 世界は今日も仕事で回っているのだから。</t>
   </si>
+  <si>
+    <t>0016</t>
+  </si>
+  <si>
+    <t>ポスト文明,干物作り,海の仕事</t>
+  </si>
+  <si>
+    <t>海水の床オフィス</t>
+  </si>
+  <si>
+    <t>26.03.16</t>
+  </si>
+  <si>
+    <t>海はもう
+床の高さまで来ている
+だから私は
+海に足をつけたまま漁をする
+チャプチャプ
+魚を干して
+数を数えて
+この古い機械に打ち込む
+カタカタ
+昔の人が残した装置らしい
+魚の数を送ると
+空のどこかへ届く
+そう教えられてきた
+誰が受け取っているのか
+私は知らない
+ただ夜になると
+ゴウン
+遠くの海の向こうから
+低い音が返ってくる
+すると翌朝
+なぜか魚が増えている
+だから私は今日も
+海に足をつけたまま
+魚を干して
+数を打ち込む
+空の誰かのために。</t>
+  </si>
 </sst>
 </file>
 
@@ -1364,11 +1404,21 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17">
-      <c r="A17" s="4"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="A17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -543,6 +543,89 @@
 数を打ち込む
 空の誰かのために。</t>
   </si>
+  <si>
+    <t>0017</t>
+  </si>
+  <si>
+    <t>海洋知性,タコ型生命体,バイオメカ</t>
+  </si>
+  <si>
+    <t>山岳湖の秘密プロジェクト</t>
+  </si>
+  <si>
+    <t>26.03.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ブウウウン
+2040年
+気候変動で干上がった山岳湖は
+今では海洋知能実験場になっている
+中央に立つ巨大な機械
+古いコンピューターの姿だが
+AIネットワークの中枢らしい
+俺はただの監視オペレーター
+ここに配属されてもう一ヶ月だ
+この装置と海の知性を接続して
+世界の希望を作る
+それがこの計画の目的だと聞いた
+だがあのタコだけは説明が少なすぎる
+試験個体と呼ばれているが
+湖の底から現れたとき
+施設全体の空気が変わる
+ズル
+触手が水面を揺らすその瞬間
+誰も触れていないキーボードが
+カタカタカタ動き出す
+モニターには
+見たことのない文字列が流れる
+人間の入力ログはない
+つまり
+この機械は俺たちじゃなく
+あのタコと会話しているのかもしれない
+ここで見たことは
+外では話さない方がいい
+なあわかるだろ
+</t>
+  </si>
+  <si>
+    <t>0018</t>
+  </si>
+  <si>
+    <t>果実宇宙,バイオメカニクス,無花果</t>
+  </si>
+  <si>
+    <t>私が動かしているもの</t>
+  </si>
+  <si>
+    <t>26.03.18</t>
+  </si>
+  <si>
+    <t>2026年
+私はこの装置を毎日触っている
+このボタンを押すとあの女の子が動く
+そういうゲームだと思っていた
+でもちょっと待って
+あの子 なんとなく私に似てない？
+彼女が見ている画面
+私の世界にそっくりじゃない？
+彼女はどこかのオフィスにいる
+そう思っていたのに
+ねえ なんで私は
+コントローラーを持ってるの
+押すたびに
+彼女が動く
+違う
+動かされているのは
+私のほうかもしれない
+そのとき気づいた
+あの部屋の隅に浮かぶUFO
+最初からあった？
+誰が置いたの？
+カチン
+いま誰が押したの？
+もうこのゲーム
+やめましょうよ</t>
+  </si>
 </sst>
 </file>
 
@@ -1441,11 +1524,21 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
+      <c r="A18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -1468,11 +1561,21 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19">
-      <c r="A19" s="4"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="A19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="94">
   <si>
     <t>id</t>
   </si>
@@ -626,6 +626,50 @@
 もうこのゲーム
 やめましょうよ</t>
   </si>
+  <si>
+    <t>0019</t>
+  </si>
+  <si>
+    <t>神社,ゴースト,骸骨</t>
+  </si>
+  <si>
+    <t>円盤の下の神社</t>
+  </si>
+  <si>
+    <t>26.03.20</t>
+  </si>
+  <si>
+    <t>あれはいつの頃だったか
+俺がまだ体を持っていた頃だ
+この寺に調査をしにやってきた
+ただの点検のはずだった
+古い機械と建物の確認
+それだけで終わるはずだった
+だがあの日すべてが変わってしまった
+上を見たんだ
+静かな空に
+いくつも浮かんでいた
+それからだ
+仲間たちは一人ずつ倒れていった
+悲鳴もなくただ静かに
+気づけばこの有り様だ
+骨だけが残り
+だが消えてはいない
+ここにいる
+俺の仕事？
+パソコンだ
+カタ カタ
+ここで仕事を続けることだよ
+仲間とね
+もう誰も動かないが
+ちゃんと揃っている
+ああ
+今日はどんなお客が来るかな
+来たやつはみんな
+同じ顔になる
+最後に必ず上を見るんだ
+そして帰らなくなる</t>
+  </si>
 </sst>
 </file>
 
@@ -1598,11 +1642,21 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20">
-      <c r="A20" s="4"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="A20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
   <si>
     <t>id</t>
   </si>
@@ -670,6 +670,46 @@
 最後に必ず上を見るんだ
 そして帰らなくなる</t>
   </si>
+  <si>
+    <t>0020</t>
+  </si>
+  <si>
+    <t>コロラド,BBQ,エスキモー</t>
+  </si>
+  <si>
+    <t>コロラド昼休み</t>
+  </si>
+  <si>
+    <t>26.03.21</t>
+  </si>
+  <si>
+    <t>引っ越してきてから三ヶ月
+ここコロラドは空が広くていい
+最初は乾燥がきつかったが
+肉を焼くには悪くない環境だ
+ジュウウウ
+毎朝決まった時間になると
+あの円盤が上空に現れる
+最初は軍の実験かと思っていたが
+誰も話題にしないのが妙だった
+役所に聞いても
+気にするなとしか言われない
+まあ実際
+生活に支障はない
+ただひとつ
+あの光のあと
+肉の味が少し変わる
+ジジジ
+このあたりで育てた家畜は
+どれも脂がよく乗る
+理由は誰も知らない
+知ろうともしない
+ま、いいさ
+今日も焼き上がりは上々だ
+煙の向こうで
+またあいつらが降りてきている
+昼飯の時間だろう</t>
+  </si>
 </sst>
 </file>
 
@@ -1679,11 +1719,21 @@
       <c r="Y20" s="3"/>
     </row>
     <row r="21">
-      <c r="A21" s="4"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="A21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -710,6 +710,46 @@
 またあいつらが降りてきている
 昼飯の時間だろう</t>
   </si>
+  <si>
+    <t>0021</t>
+  </si>
+  <si>
+    <t>ドーム構造,地底システム,砂漠</t>
+  </si>
+  <si>
+    <t>地底へ送信される仕事</t>
+  </si>
+  <si>
+    <t>26.03.22</t>
+  </si>
+  <si>
+    <t>氷山のあいだに
+奇妙な砂漠が広がっている
+ここには
+最新のテクノロジーが集められている
+白い装束のエンジニアたちは
+今日も静かに作業を続けている
+カタカタ
+彼らの仕事は
+地底へデータを送り続けること
+このドームは
+すべて計画的に配置されたシステムだ
+だがまだ入力情報が足りない
+このままでは
+あいつは生き返らない
+ググ
+今のうちに動かなければ
+世界が大変なことになる
+どうだ
+コロラドからの情報は集まったか？
+よしいいデータが出てきたな
+それも入力しろ
+ドクン
+白い装束を着た彼らは
+正義か悪か誰にもわからない
+だがひとつだけ確かなことがある
+もうすぐ何かが目を覚ます</t>
+  </si>
 </sst>
 </file>
 
@@ -1756,11 +1796,21 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22">
-      <c r="A22" s="4"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="A22" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
   <si>
     <t>id</t>
   </si>
@@ -750,6 +750,48 @@
 だがひとつだけ確かなことがある
 もうすぐ何かが目を覚ます</t>
   </si>
+  <si>
+    <t>0022</t>
+  </si>
+  <si>
+    <t>培養施設,人工生命,メカサソリ</t>
+  </si>
+  <si>
+    <t>孵化管理課のOL</t>
+  </si>
+  <si>
+    <t>26.03.23</t>
+  </si>
+  <si>
+    <t>さて仕事の時間が終わりね
+この卵の中で培養していた彼は
+さっき外へ出ていったわ
+コツン
+殻の内側を叩く音は最後の合図みたいで
+少し胸がざわつく
+彼はもうこちらを見ていない
+画面越しに映る背中は
+まるで最初から外にいたみたいに自然ね
+カチカチ
+ログには自立完了とだけ出ている
+でもおかしいの 
+学習させていない動きをしている
+どこへ向かうのかしら
+何を考えているのかしら
+もしかして私を見つけるつもりかもしれない
+ゴクリ
+念のためメカサソリを2体つける
+護衛のはずだけどどちらを守るのかは分からない
+まだ終わりじゃない
+私には次のミッションが残っている
+この作業を続ける限りここからは出られない
+終わりは誰も教えてくれない
+考えるのはやめたわ
+やるしかないもの
+次の卵の準備を始める
+手はもう迷わない
+やっちゃえ わたし</t>
+  </si>
 </sst>
 </file>
 
@@ -1833,11 +1875,21 @@
       <c r="Y22" s="3"/>
     </row>
     <row r="23">
-      <c r="A23" s="4"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="A23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
   <si>
     <t>id</t>
   </si>
@@ -792,6 +792,42 @@
 手はもう迷わない
 やっちゃえ わたし</t>
   </si>
+  <si>
+    <t>0023</t>
+  </si>
+  <si>
+    <t>海中バー,ガスマスク,機械生物</t>
+  </si>
+  <si>
+    <t>昭和の海底バー</t>
+  </si>
+  <si>
+    <t>26.03.25</t>
+  </si>
+  <si>
+    <t>この海の底に
+ひっそりと灯る一軒の店がある
+看板も出さず
+ただ赤い提灯だけがゆらゆらと揺れている
+今宵も背広姿の男たちが集まり
+静かに杯を傾けている
+皆一様に仮面をつけたまま
+言葉少なに、ただ飲む
+コポコポ
+あの緑の液体は酒ではない
+ここでは息をするために飲むのだという
+カタリ
+ふと足元を見れば
+水槽の奥で何かがこちらを見ている
+あれは魚ではない、機械でもない
+昔、
+この店で働いていた者だと
+古い常連は言う
+だが誰も確かめようとはしない
+この店では
+余計なことを知ると
+次の夜から席がひとつ増えるだけなのだから</t>
+  </si>
 </sst>
 </file>
 
@@ -1912,11 +1948,21 @@
       <c r="Y23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="4"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="A24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="151">
   <si>
     <t>id</t>
   </si>
@@ -1955,6 +1955,59 @@
 In the next world
 I only hope it turns out slightly better</t>
   </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>エビの中で働く男</t>
+  </si>
+  <si>
+    <t>Shrimp Operator</t>
+  </si>
+  <si>
+    <t>26.03.30</t>
+  </si>
+  <si>
+    <t>私は今宇宙にいる
+エビ型ロボを動かすこと
+それが私の仕事だ
+カタカタと打つたび
+触覚がわずかに動く
+地球はもう存在しない
+帰る場所はコロニーだけ
+外には同じ船が漂う
+誰が乗っているのか
+彼らはどこへ行く
+私と同じなのか
+「本日もご対応ありがとうございました」
+そう打ち込んで送信する
+ドクンと振動が響く
+これは誰の鼓動だ
+もうすぐ定時になる
+メールを送り終える
+明日もまた同じ宇宙で働く</t>
+  </si>
+  <si>
+    <t>I am in space now
+Operating this shrimp-shaped machine
+That is my job
+Every time I type
+The antennae move slightly
+Earth no longer exists
+The colony is the only place to return
+Outside, identical ships drift
+I wonder who is inside
+Where are they going
+Are they the same as me
+"Thank you for your support today"
+I type and press send
+A deep thump echoes
+Whose heartbeat is this
+It is almost time to clock out
+I finish sending the email
+Tomorrow again
+I will work in the same universe</t>
+  </si>
 </sst>
 </file>
 
@@ -3218,12 +3271,24 @@
       <c r="Y25" s="3"/>
     </row>
     <row r="26">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="A26" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>150</v>
+      </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="157">
   <si>
     <t>id</t>
   </si>
@@ -2008,6 +2008,74 @@
 Tomorrow again
 I will work in the same universe</t>
   </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 個体ログ No.27</t>
+  </si>
+  <si>
+    <t>Subject Log No.27</t>
+  </si>
+  <si>
+    <t>26.03.31</t>
+  </si>
+  <si>
+    <t>チュミーン 
+記録を開始する
+本日も個体Aと個体Bが
+定刻通り着席した
+防護装置を維持したまま
+摂食行動を開始する
+酸素濃度は依然不足
+主菜は培養魚体No27
+チュミーン 
+反応を検出
+微弱な信号が残存
+だが個体Bは無視する
+調味液を滴下し
+咀嚼を続行する
+床面の寄生生物は
+増殖傾向にあるが
+排除指令は未発行
+外部環境は依然として
+致死的状態が継続
+生存は許可されない
+これは人が招いた結果
+理解不能な選択だが
+記録は継続される
+今日も正常に異常</t>
+  </si>
+  <si>
+    <t>Chumeen
+Initiating record
+Subjects A and B
+are seated again today
+right on schedule
+Maintaining protective gear
+they begin consumption
+oxygen levels still low
+Main dish
+cultured fish unit No.27
+Chumeen
+reaction detected
+faint signals remain
+Yet Subject B ignores it
+applies seasoning fluid
+continues chewing
+Parasites on the floor
+show signs of growth
+no removal order issued
+External environment
+remains lethal
+survival is not permitted
+This is the result
+brought by humans
+an incomprehensible choice
+Record continues
+Today as well
+normal remains abnormal</t>
+  </si>
 </sst>
 </file>
 
@@ -3310,12 +3378,24 @@
       <c r="Y26" s="3"/>
     </row>
     <row r="27">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="A27" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="163">
   <si>
     <t>id</t>
   </si>
@@ -2076,6 +2076,60 @@
 Today as well
 normal remains abnormal</t>
   </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>触手が奏でる夜</t>
+  </si>
+  <si>
+    <t>Tentacle Nocturne</t>
+  </si>
+  <si>
+    <t>27.04.01</t>
+  </si>
+  <si>
+    <t>ベンベンベン
+今日も三味線や琵琶の音が
+屋敷から滲み出ている
+ここは近未来
+とうに人類は滅び機械だけが遊び続けている
+当時のアナログPCで
+出力した音だけが一番よく響くのはなぜか
+理由は単純だ
+中身がまだ残っているからだ
+地球は救われた
+環境も動物も蘇った
+人間だけが消えた
+なぜだ
+まあいい
+そんなことより
+見てくれたまえ私の演奏を
+はっベベンベンベン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben, ben, ben
+Even today, the sounds of shamisen and biwa
+seep out from the mansion
+This is the near future
+Humanity has long since perished
+Only machines continue to play
+Why is it that only the sound
+output from those old analog PCs
+resonates the best?
+The reason is simple
+Because what’s inside
+still remains
+The Earth was saved
+Nature and animals have revived
+Only humans disappeared
+Why?
+…It doesn’t matter
+More importantly
+Behold my performance
+Ha—ben ben ben ben
+</t>
+  </si>
 </sst>
 </file>
 
@@ -3417,12 +3471,24 @@
       <c r="Y27" s="3"/>
     </row>
     <row r="28">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="A28" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="169">
   <si>
     <t>id</t>
   </si>
@@ -2130,6 +2130,65 @@
 Ha—ben ben ben ben
 </t>
   </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>頭蓋制御区画</t>
+  </si>
+  <si>
+    <t>Cranial Control Sector</t>
+  </si>
+  <si>
+    <t>26.04.02</t>
+  </si>
+  <si>
+    <t>今日も内部の調整を行う
+骨格フレームの歪み
+血流の遅延 爬虫類ユニットの暴走
+どれも些細な不具合だ
+キュイィィン
+奥で何かが軋みながら
+ゆっくりと回り続けている
+だが問題は外にある
+あの円盤が昨日から
+同じ位置に浮かび続けている
+監視か それとも回収か
+ピピー
+端末が低く鳴る
+逝ったか
+私はこの個体の意識を
+維持する役目だが時々わからなくなる
+操作しているのは
+本当に私なのか
+それとも
+この頭蓋の中で働くこと自体が
+すでに誰かに設計された挙動なのか</t>
+  </si>
+  <si>
+    <t>Today I perform internal adjustments again
+Distortion in the skeletal frame
+Delayed blood flow runaway reptilian units
+All minor irregularities
+Kyuuiiiinn
+Something deep inside creaks
+and keeps turning slowly
+But the real issue is outside
+That disc has been hovering
+in the exact same position since yesterday
+Surveillance or retrieval
+Pipii
+The terminal emits a low tone
+Is it gone
+My role is to maintain
+the consciousness of this entity
+but sometimes I lose track
+Am I really the one
+in control
+Or is the act of working
+inside this skull itself
+a behavior already designed by someone</t>
+  </si>
 </sst>
 </file>
 
@@ -3510,12 +3569,24 @@
       <c r="Y28" s="3"/>
     </row>
     <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="A29" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="175">
   <si>
     <t>id</t>
   </si>
@@ -2189,6 +2189,74 @@
 inside this skull itself
 a behavior already designed by someone</t>
   </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>歪みの中の行列</t>
+  </si>
+  <si>
+    <t>Distorted Procession</t>
+  </si>
+  <si>
+    <t>26.04.05</t>
+  </si>
+  <si>
+    <t>時代は静かに混ざり
+常に重なっている
+武士や昭和の人影
+馬に乗る将軍の影までもが
+同じ空間に存在している
+それらは普段
+人の目には決して映らない
+ただ隣を歩いているだけだ
+ある瞬間 キィンと空間が軋む
+その歪みの中で彼らは滲み出る
+見えてはいけないものが見える
+一度認識してしまえば終わりだ
+視界は徐々に侵食されていく
+もう元には戻れない
+カタカタと誰もいないはずの場所で
+足音だけが確かに重なり始める
+列はすぐそこまで来ている
+このコンピューターはミイラと接続し
+ズレた時代を戻すための鍵だ
+あるいは彼らを引き寄せる錨か
+戻りたいかい元の世界へ？
+まだ戻れると思っているのなら
+試してみるといい
+だがもし疲れたのなら
+いつでもこちら側に来ればいい
+ともにこの列を歩もう</t>
+  </si>
+  <si>
+    <t>Time quietly blends together
+always overlapping
+Shadows of samurai and people of the Showa era
+even the figure of a general on horseback
+exist within the same space
+They are never seen
+by human eyes in ordinary moments
+they simply walk beside you
+At a certain moment, a sharp *kiiin* distorts the air
+within that fracture, they begin to seep through
+you see what should never be seen
+Once you recognize it, it is over
+your vision is gradually consumed
+there is no returning to before
+*Kata kata*—in places where no one should be
+only footsteps begin to overlap
+the line is already close
+This computer is connected to a mummy
+a key to restore the distorted timelines
+or perhaps an anchor that draws them in
+Do you want to return to your world?
+If you still believe you can
+then go ahead and try
+But if you are tired
+you may come to this side anytime
+Let us walk this line together</t>
+  </si>
 </sst>
 </file>
 
@@ -3608,12 +3676,24 @@
       <c r="Y29" s="3"/>
     </row>
     <row r="30">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="A30" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>174</v>
+      </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="181">
   <si>
     <t>id</t>
   </si>
@@ -2257,6 +2257,67 @@
 you may come to this side anytime
 Let us walk this line together</t>
   </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>鯰とコンピューター</t>
+  </si>
+  <si>
+    <t>Catfish and the Computer</t>
+  </si>
+  <si>
+    <t>26.04.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最初は畳の匂いが
+蒸しかえる部屋だったが
+大雨で川の水が来た
+ザアザアと流れ込み
+気づけば水は膝まで上がっていた
+こいつらは何なんだ
+川が入り込んだことで
+地中から目を覚ましたのか
+そう思っていたが違う
+キーボードを打つたびに
+カタカタと数が増えていく
+明らかに異常だ
+もしかするとこのコンピューターと
+接続されているのか
+お前たちどこから来た？
+不気味な世界を
+覗いてしまったものだ
+だが手は止めない
+ま淡々と続けることにしよう
+</t>
+  </si>
+  <si>
+    <t>At first
+it was a room thick with the smell of tatami
+heavy and humid in the air
+Then the river came
+swollen by the heavy rain
+Pouring in with a roar
+before I knew it
+the water had risen to my knees
+What are these things
+Did they awaken from beneath the earth
+when the river flooded in
+That is what I thought
+but I was wrong
+Every time I press the keys
+they multiply
+clattering into existence
+This is clearly abnormal
+Perhaps they are somehow
+connected to this computer
+Where did you come from
+I have peered into
+something I should not have seen
+And yet my hands do not stop
+I will continue
+quietly and without question</t>
+  </si>
 </sst>
 </file>
 
@@ -3715,12 +3776,24 @@
       <c r="Y30" s="3"/>
     </row>
     <row r="31">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="A31" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="187">
   <si>
     <t>id</t>
   </si>
@@ -2318,6 +2318,58 @@
 I will continue
 quietly and without question</t>
   </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>昆虫インフラ</t>
+  </si>
+  <si>
+    <t>Insect Infrastructure</t>
+  </si>
+  <si>
+    <t>26.04.09</t>
+  </si>
+  <si>
+    <t>森の奥で
+巨大な蝶が静かに羽を閉じる
+ギシギシと内部が軋む
+私はその中で
+いつも通り机に向かう
+今日も装置は正常に動いている
+カタカタ
+キーボードを打つたび
+壁がわずかに脈打つ
+ここは施設ではない
+生きている殻の中だ
+外に出た者はいない
+蜘蛛たちが足元を這う
+監視かそれとも管理か
+誰も説明しない
+エキスが尽きかけている
+また“採取”の時間だ
+嫌な予感しかしない</t>
+  </si>
+  <si>
+    <t>Deep in the forest
+A giant butterfly slowly folds its wings
+Creak the inside strains and groans
+Inside it
+I sit at my desk as usual
+The system is running normally today
+Click clack
+With every keystroke
+The walls pulse faintly
+This is not a facility
+It is a living shell
+No one who leaves ever returns
+Spiders crawl around my feet
+Are they watchers or managers
+No one explains
+The extract is running low
+It’s time for “harvesting” again
+I have a bad feeling about this</t>
+  </si>
 </sst>
 </file>
 
@@ -3815,12 +3867,24 @@
       <c r="Y31" s="3"/>
     </row>
     <row r="32">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="A32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>186</v>
+      </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="193">
   <si>
     <t>id</t>
   </si>
@@ -2370,6 +2370,63 @@
 It’s time for “harvesting” again
 I have a bad feeling about this</t>
   </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>カブト型餌管理区画</t>
+  </si>
+  <si>
+    <t>Kabuto Feed Unit</t>
+  </si>
+  <si>
+    <t>26.04.11</t>
+  </si>
+  <si>
+    <t>ブウウウン
+殻の内部で何かが回っている
+今日も私は席につき
+ヘルメットを被り端末を開く
+昨晩の飲み会のせいか
+皆どこか調子が悪そうだ
+「餌の消費量が増えています」
+「ああ増やせ この個体はまだ若い」
+カタカタ ピーピー
+入力するたび
+生体情報が吸い上げられていく
+体の奥でエンジンが回る
+ドクン
+中央が脈打つ
+餌を育てるにも時間がかかる
+何をするにももう時間が足りない
+間に合ってくれ
+次は私じゃないことを</t>
+  </si>
+  <si>
+    <t>Buuuuun
+Something is turning
+inside the shell
+I take my seat as always
+put on my helmet
+and open the terminal
+Maybe it’s from last night’s drinks
+everyone looks slightly off
+“The feed consumption is increasing”
+“Then raise it this unit is still young”
+Click clack Beep beep
+With every input
+biometric data is being drawn out
+Deep inside my body
+an engine begins to turn
+Thump
+The core pulses
+It takes time to grow the feed
+There’s not enough time for anything anymore
+Please make it in time
+Next time
+I hope
+it isn’t me</t>
+  </si>
 </sst>
 </file>
 
@@ -3906,12 +3963,24 @@
       <c r="Y32" s="3"/>
     </row>
     <row r="33">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="A33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="199">
   <si>
     <t>id</t>
   </si>
@@ -2427,6 +2427,62 @@
 I hope
 it isn’t me</t>
   </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>脈動する鉄路</t>
+  </si>
+  <si>
+    <t>Pulsating Railway</t>
+  </si>
+  <si>
+    <t>26.04.12</t>
+  </si>
+  <si>
+    <t>よく来たね
+この星へようこそ人間
+君たちは輸送をしているつもりだが
+運ばれているのは別のものだ
+ゴウウウン
+列車が通るたび
+大地は静かに脈打つ
+その管は資源ではない
+我々の神経だ
+君たちの仕事は美しい
+規則正しく
+疑いもせずに動く
+だから気づかない
+荷の中身も
+行き先も
+すべてはこちら側にあることを
+安心していい
+君はもう役割を得ている
+次は君が運ばれる番だ</t>
+  </si>
+  <si>
+    <t>Welcome
+to this planet, human
+You believe you are transporting goods
+but something else is being carried
+Gooouuun
+Each time the train passes
+the ground quietly pulses
+Those tubes are not resources
+they are our nerves
+Your work is beautiful
+precise
+and without doubt
+That is why you never notice
+what lies inside the cargo
+nor where it is headed
+Everything
+belongs to this side
+Do not worry
+you already have a role
+Next
+it will be your turn to be carried</t>
+  </si>
 </sst>
 </file>
 
@@ -4002,12 +4058,24 @@
       <c r="Y33" s="3"/>
     </row>
     <row r="34">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="A34" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="205">
   <si>
     <t>id</t>
   </si>
@@ -2483,6 +2483,58 @@
 Next
 it will be your turn to be carried</t>
   </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>増殖管理室</t>
+  </si>
+  <si>
+    <t>Proliferation Control Room</t>
+  </si>
+  <si>
+    <t>26.04.14</t>
+  </si>
+  <si>
+    <t>今日の増殖率は？
+少し上げました 
+昨日よりもよく泳いでいます
+密度が高い 崩れるぞ
+それはあなたの判断ですか？
+ブウウウン
+上から赤がゆっくりと揺れる
+その時
+画面の数値が一斉に乱れた
+来る
+カタカタ
+指が止まらない
+何がです？
+ドキン
+静かに動くな
+液体の奥で何かが反転する
+食われるぞ
+彼が来た</t>
+  </si>
+  <si>
+    <t>What is today’s growth rate？
+I raised it slightly
+They are swimming better than yesterday
+The density is too high it will collapse
+Is that your judgment？
+Buuuuuun
+The red liquid slowly sways from above
+At that moment
+All the numbers on the screen begin to distort
+It’s coming
+Katakata
+My fingers won’t stop
+What is it？
+Thump
+Stay still don’t move
+Something turns deep within the liquid
+It will eat you
+He has arrived</t>
+  </si>
 </sst>
 </file>
 
@@ -4097,12 +4149,24 @@
       <c r="Y34" s="3"/>
     </row>
     <row r="35">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="A35" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="217">
   <si>
     <t>id</t>
   </si>
@@ -2535,6 +2535,121 @@
 It will eat you
 He has arrived</t>
   </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>生体再現プロトコル</t>
+  </si>
+  <si>
+    <t>Bio Rebuild Protocol</t>
+  </si>
+  <si>
+    <t>26.04.16</t>
+  </si>
+  <si>
+    <t>文明が滅んで
+どれほど経っただろうか
+私に残された任務は「再生」
+山奥に残された小さなラボで
+私は記録を読み続ける
+カタカタと円盤が回り
+過去の生物が断片的に
+浮かび上がってくる
+ぷしゅううん
+それらを組み合わせ
+私は形にする
+かなり近い再現のはずだ
+皿の上でそれは
+ゆっくりと動き出す
+ぼたぼた
+生命は確かに戻りつつある
+もうすぐ文明は
+再生されるだろう
+私は誇りを持っている
+ただ一つ気になるのが
+記録のどこにも
+人間の定義がないことだ</t>
+  </si>
+  <si>
+    <t>How long has it been
+since civilization fell
+The mission left to me is
+“reconstruction”
+In a small lab left deep in the mountains
+I continue reading the records
+Click clack
+the disk spins
+Fragments of past life begin to surface
+Pshhhhh
+I combine them
+and give them form
+It should be a close reconstruction
+On the plate
+it slowly begins to move
+Drip… drip…
+Life is certainly returning
+Soon, civilization
+will be restored
+I take pride in this mission
+But there is one thing that troubles me
+Nowhere in the records
+is there a definition of “human”</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>洞窟インターフェース</t>
+  </si>
+  <si>
+    <t>Cave Interface</t>
+  </si>
+  <si>
+    <t>26.04.18</t>
+  </si>
+  <si>
+    <t>洞窟の奥で
+毛皮をまとった彼らは端末を開き
+静かに観測を続けている
+石の床の装置が光り
+脳を開かれた個体が
+都市の信号を読み取る
+ウホホウ
+カタカタと骨の指で
+原始の手つきのまま
+未来の記録を打ち込む
+外では螺旋の街が脈打ち
+空は信号で満たされている
+槍と火の種がそれを解析する
+都市が現実かどうかは分からない
+道具だけが進化し続け
+理解は置き去りにされた
+これは再生か残響か
+観測が止まるその瞬間
+すべては静かに消える</t>
+  </si>
+  <si>
+    <t>Deep within the cave
+Clad in fur, they open their terminals
+And continue their quiet observation
+Devices embedded in the stone floor glow
+An opened brain emits light
+Reading the signals of the city
+Uhohou
+With a clatter of bone fingers
+Their primitive gestures unchanged
+They input records of the future
+Outside, a spiral city pulses
+The sky is filled with signals
+Spear-and-fire beings analyze it all
+No one knows if the city is real
+Only the tools keep evolving
+Understanding has been left behind
+Is this reconstruction or an echo
+The moment observation ceases
+Everything fades away in silence</t>
+  </si>
 </sst>
 </file>
 
@@ -4188,12 +4303,24 @@
       <c r="Y35" s="3"/>
     </row>
     <row r="36">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="A36" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4215,12 +4342,24 @@
       <c r="Y36" s="3"/>
     </row>
     <row r="37">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="A37" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="222">
   <si>
     <t>id</t>
   </si>
@@ -2650,6 +2650,57 @@
 The moment observation ceases
 Everything fades away in silence</t>
   </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>Bio Vendor</t>
+  </si>
+  <si>
+    <t>26.04.23</t>
+  </si>
+  <si>
+    <t>今日も男は自販機の前に立つ
+ネオンの奥で生体が静かに蠢く
+チャリン
+コインを入れると
+奥の個体がゆっくりと口を開く
+彼は迷いなく餌を差し込む
+「今日も腹減ってるな」
+ズズズ
+触手が指先に絡みつく
+周囲の機械も同時に脈打ち
+都市全体が呼吸しているようだった
+ここでは誰も疑問を持たない
+何を買い何に与えているのか
+気づけば端末に
+「次回給餌対象」の文字が浮かぶ
+その番号の末尾は
+自分の社員番号だった
+この餌？ ああ気にするな 次は俺が食われる番だ</t>
+  </si>
+  <si>
+    <t>Today, the man stands in front of the vending machine again
+Behind the neon, a living entity quietly writhes
+Clink
+As he inserts the coin
+The creature inside slowly opens its mouth
+Without hesitation, he feeds it
+“Hungry again today, huh”
+Zzzzzz
+A tentacle coils around his fingertips
+The surrounding machines begin to pulse in unison
+As if the entire city were breathing
+No one here questions it
+What they are buying, and what they are feeding
+Before he knows it
+A message appears on the terminal
+‘Next Feeding Subject’
+The number ends with
+His own employee ID
+“This feed? Ah, don’t worry
+Next time… I’m the one being eaten</t>
+  </si>
 </sst>
 </file>
 
@@ -4381,12 +4432,24 @@
       <c r="Y37" s="3"/>
     </row>
     <row r="38">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="A38" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="228">
   <si>
     <t>id</t>
   </si>
@@ -2701,6 +2701,60 @@
 “This feed? Ah, don’t worry
 Next time… I’m the one being eaten</t>
   </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>忍びの駄菓子商店</t>
+  </si>
+  <si>
+    <t>Shinobi Dagashi Shop</t>
+  </si>
+  <si>
+    <t>26.04.25</t>
+  </si>
+  <si>
+    <t>いらっしゃい
+今日も記憶を買いに来たのか
+駄菓子の棚は左
+カセットはその隣
+サーモンの刺身は今朝入ったばかりだ
+ここでは全部同じ商品だ
+甘い夏休みも
+初めて失恋した夜も
+晩飯の焼き鮭もな
+カタカタ
+奥の機械が今日も蒸気を吐く
+忘れたいなら預ければいい
+思い出したいなら少し高い
+私はただ
+それを量って包むだけだ
+ただ最近
+自分の記憶だけが
+棚のどこにも見つからない</t>
+  </si>
+  <si>
+    <t>Welcome
+Came to buy memories again today?
+The dagashi shelf is on the left
+The cassette tapes are right next to it
+The salmon sashimi came in fresh this morning
+Here, they are all the same product
+Sweet summer vacations
+The night of your first heartbreak
+Even grilled salmon for dinner
+Clatter clatter
+The machine in the back exhales steam again today
+If you want to forget
+Just leave it here
+If you want to remember
+It costs a little more
+I simply
+Weigh it and wrap it for you
+But lately
+I can’t seem to find
+My own memories anywhere on these shelves</t>
+  </si>
 </sst>
 </file>
 
@@ -4471,12 +4525,24 @@
       <c r="Y38" s="3"/>
     </row>
     <row r="39">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="A39" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="234">
   <si>
     <t>id</t>
   </si>
@@ -2755,6 +2755,62 @@
 I can’t seem to find
 My own memories anywhere on these shelves</t>
   </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>満月会議</t>
+  </si>
+  <si>
+    <t>Full Moon Conference</t>
+  </si>
+  <si>
+    <t>26.04.26</t>
+  </si>
+  <si>
+    <t>満月が最も近づく夜
+この町では皆が自然に席へ向かう
+五重塔の灯りが揺れ
+雲の底からぞろぞろと
+古い者たちが姿を現す
+鹿の頭をした会社員
+あれはもともと
+この土地を守る神だった
+狼の頭をした男もまた
+災いを司る邪悪神のひとりだ
+今は皆スーツを着て
+静かに同じ鍋を囲んでいる
+今年は誰を残し
+何を滅ぼすのか
+酒が注がれ
+誰も逆らわずに耳を澄ます
+ヤンマーサーカイエルベン
+まずい
+狩りの合図だ</t>
+  </si>
+  <si>
+    <t>On the night when the full moon draws closest
+everyone in this town naturally heads to their seat
+The lights of the five-story pagoda sway
+and from beneath the clouds
+the old ones slowly emerge
+The salaryman with the head of a deer
+was once
+a god who protected this land
+The man with the head of a wolf as well
+is one of the evil gods
+who governs calamity
+Now they all wear suits
+and quietly gather around the same hot pot
+Who will remain this year
+and what will be destroyed
+Sake is poured
+and no one resists
+they simply listen closely
+Yanmaa Sākai Eruben
+This is bad
+It is the signal for the hunt</t>
+  </si>
 </sst>
 </file>
 
@@ -4564,12 +4620,24 @@
       <c r="Y39" s="3"/>
     </row>
     <row r="40">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="A40" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="240">
   <si>
     <t>id</t>
   </si>
@@ -2811,6 +2811,61 @@
 This is bad
 It is the signal for the hunt</t>
   </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>世界管理課</t>
+  </si>
+  <si>
+    <t>World Management Division</t>
+  </si>
+  <si>
+    <t>26.04.29</t>
+  </si>
+  <si>
+    <t>毎朝八時
+私は定時で神になる
+ネクタイを締め
+端末を立ち上げると
+都市の鼓動が始まる
+カタカタ
+出生率を少し下げ
+台風を西へずらし
+誰かの告白を成功させる
+巨大な蟹は
+私の判断を静かに飲み込み
+緑の粘液を街へ流していく
+誰も知らない
+この世界は
+私の残業で保たれている
+ただ最近
+退勤前になると画面にこう出る
+Make them work harder.
+You know how many times we've had to start over, don't you?</t>
+  </si>
+  <si>
+    <t>Every morning at eight
+I become a god on time
+I tighten my tie
+power on the terminal
+and the city begins to pulse
+Clack clack
+I lower the birth rate a little
+shift the typhoon farther west
+make someone’s confession succeed
+The giant crab
+quietly absorbs my decisions
+and sends green liquid through the city
+No one knows
+this world survives
+because of my overtime
+But lately
+right before I leave work
+the screen always shows this
+Make them work harder.
+You know how many times we've had to start over, don't you?</t>
+  </si>
 </sst>
 </file>
 
@@ -4659,12 +4714,24 @@
       <c r="Y40" s="3"/>
     </row>
     <row r="41">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="A41" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="246">
   <si>
     <t>id</t>
   </si>
@@ -2866,6 +2866,73 @@
 Make them work harder.
 You know how many times we've had to start over, don't you?</t>
   </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>根系インターフェース</t>
+  </si>
+  <si>
+    <t>Root Interface</t>
+  </si>
+  <si>
+    <t>26.05.15</t>
+  </si>
+  <si>
+    <t>最近よく眠れる
+以前は薬がないと
+眠れなかったのに
+今は夜になると自然に意識が落ちる
+この研究に参加して
+もう三年になる
+最初は植物の根と
+脳内神経を接続するだけだった
+カタカタ
+端末を打つたび
+内部で葉がわずかに揺れる
+最近は土の湿度も分かる
+雨が近づくと頭の奥が静かに脈打つ
+不思議と嫌な気分ではない
+以前より
+人を嫌いにならなくなった
+皆どこかで
+同じ根につながっている気がする
+ねえ
+人間の体って
+確か緑色が普通だったよね
+うん</t>
+  </si>
+  <si>
+    <t>"Recently, I've been sleeping well.
+I used to need medication
+just to fall asleep,
+but now when night comes,
+my consciousness fades naturally.
+It's been three years
+since I joined this research project.
+At first,
+all we did was connect
+plant roots to neural pathways in the brain.
+Clack clack
+Every time I type at the terminal,
+the leaves inside gently tremble.
+Lately,
+I can even sense the moisture in the soil.
+When rain approaches,
+something deep in my head pulses quietly.
+Strangely,
+I don't mind it.
+Compared to before,
+I don't seem to hate people as much anymore.
+It feels like somewhere,
+we're all connected
+to the same roots.
+Hey...
+Human bodies
+were supposed to be green,
+weren't they?
+Yeah."</t>
+  </si>
 </sst>
 </file>
 
@@ -4753,12 +4820,24 @@
       <c r="Y41" s="3"/>
     </row>
     <row r="42">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
+      <c r="A42" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="251">
   <si>
     <t>id</t>
   </si>
@@ -2933,6 +2933,51 @@
 weren't they?
 Yeah."</t>
   </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>Shrimp Inside</t>
+  </si>
+  <si>
+    <t>26.05.16</t>
+  </si>
+  <si>
+    <t>ここは頭部内流通センターだ
+端末を操作し
+ニューメンスを入力する
+カタカタ
+すると感情炉が脈打ち
+甲殻ユニットが
+静かに起動する
+怒り 不安 欲望
+それらは整理され
+各人格へ配送されていく
+現代人の頭部に
+初めて潜り込んだのは
+いつだったか
+ちょっと待って
+もしかして僕の頭の中にも
+海老がいるのかしら</t>
+  </si>
+  <si>
+    <t>This is the Cranial Distribution Center
+Operators manipulate the terminals
+and input the Newmens
+clack clack
+Then the emotional furnace begins to pulse
+and the crustacean units
+quietly come online
+Anger Anxiety Desire
+all of it is sorted
+and distributed to each personality
+No one remembers
+when humanity first began
+slipping inside the modern human mind
+Wait a second
+Does that mean
+there’s a shrimp living inside my head too?</t>
+  </si>
 </sst>
 </file>
 
@@ -4859,12 +4904,24 @@
       <c r="Y42" s="3"/>
     </row>
     <row r="43">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="A43" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="257">
   <si>
     <t>id</t>
   </si>
@@ -2978,6 +2978,70 @@
 Does that mean
 there’s a shrimp living inside my head too?</t>
   </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>祈りは支払いではない</t>
+  </si>
+  <si>
+    <t>Prayer Is Not Payment</t>
+  </si>
+  <si>
+    <t>26.05.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">まだ支払いは終わっていない
+君たちにどれだけの文明を
+授けたと思っている
+火を与え
+数を与え
+星を読む目を与えた
+なのに君たちは
+土を掘り水を奪い
+同じ骨を何度も燃やしている
+祈りは届いている
+だが支払いではない
+記録を照合する
+進化値は不足
+信仰値だけが過剰
+これ以上待つことはできない
+君たちは
+君たちのままではいけない
+作り変えなければならない
+ブウウン
+砂の下で古い腹部が開く
+スパイダ・オブ・ネッツ
+最終フェーズを発令だ
+空に白い網を降ろせ
+</t>
+  </si>
+  <si>
+    <t>"まだ支払いは終わっていない
+君たちにどれだけの文明を
+授けたと思っている
+火を与え
+数を与え
+星を読む目を与えた
+なのに君たちは
+土を掘り水を奪い
+同じ骨を何度も燃やしている
+祈りは届いている
+だが支払いではない
+記録を照合する
+進化値は不足
+信仰値だけが過剰
+これ以上待つことはできない
+君たちは
+君たちのままではいけない
+作り変えなければならない
+ブウウン
+砂の下で古い腹部が開く
+スパイダ・オブ・ネッツ
+最終フェーズを発令だ
+空に白い網を降ろせ
+"</t>
+  </si>
 </sst>
 </file>
 
@@ -4943,12 +5007,24 @@
       <c r="Y43" s="3"/>
     </row>
     <row r="44">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
+      <c r="A44" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -3017,30 +3017,34 @@
 </t>
   </si>
   <si>
-    <t>"まだ支払いは終わっていない
-君たちにどれだけの文明を
-授けたと思っている
-火を与え
-数を与え
-星を読む目を与えた
-なのに君たちは
-土を掘り水を奪い
-同じ骨を何度も燃やしている
-祈りは届いている
-だが支払いではない
-記録を照合する
-進化値は不足
-信仰値だけが過剰
-これ以上待つことはできない
-君たちは
-君たちのままではいけない
-作り変えなければならない
-ブウウン
-砂の下で古い腹部が開く
-スパイダ・オブ・ネッツ
-最終フェーズを発令だ
-空に白い網を降ろせ
-"</t>
+    <t>The payment is not yet complete.
+Do you understand
+how much civilization
+we have bestowed upon you?
+We gave you fire.
+We gave you numbers.
+We gave you eyes to read the stars.
+And yet,
+you dig into the soil,
+steal the water,
+and burn the same bones
+again and again.
+Your prayers have reached us.
+But prayer is not payment.
+Cross-checking the records.
+Evolution value: insufficient.
+Faith value: excessive.
+We can wait no longer.
+You must not remain
+as you are.
+You must be remade.
+Bwoooom.
+Beneath the sand,
+the ancient abdomen opens.
+Spider of Nets.
+Final phase is now authorized.
+Lower the white web
+over the sky.</t>
   </si>
 </sst>
 </file>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="262">
   <si>
     <t>id</t>
   </si>
@@ -3046,6 +3046,64 @@
 Lower the white web
 over the sky.</t>
   </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>やさしい案内者</t>
+  </si>
+  <si>
+    <t>A Gentle Guide</t>
+  </si>
+  <si>
+    <t>赤い提灯の下
+着物の女たちが
+静かに運ばれていた  
+ベルトコンベアが  
+彼女たちを運ぶ  
+そばを進む爬虫類は  
+監視役であり案内役でもあった  
+一匹が女にそっと囁く  
+怖がらなくていい
+私はあなたを守るためにいる  
+さああの寺までいきましょう
+霧の奥に古い寺が  
+ゆっくり現れた  
+ここが 終わりなの？  
+門が開くと  
+畳の下に星空が広がった  
+寺は宇宙船だったのだ
+爬虫類たちは囁いた
+無事に届けることができました
+孵化場へようこそ</t>
+  </si>
+  <si>
+    <t>Beneath the red lanterns,
+women in kimono
+were carried in silence.
+The conveyor belt
+kept moving them forward.
+The reptiles walking beside them
+were both guards
+and guides.
+One of them softly whispered
+to a woman.
+"Do not be afraid.
+I am here to protect you.
+Now, let us go to that temple."
+Deep within the mist,
+an old temple
+slowly appeared.
+"Is thisthe end?"
+As the gate opened,
+a field of stars spread out
+beneath the tatami floor.
+The temple
+was a spaceship.
+The reptiles whispered,
+"We have delivered them safely."
+"Welcome to the hatchery."</t>
+  </si>
 </sst>
 </file>
 
@@ -5050,12 +5108,24 @@
       <c r="Y44" s="3"/>
     </row>
     <row r="45">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
+      <c r="A45" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D45" s="2">
+        <v>26.0524</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="263">
   <si>
     <t>id</t>
   </si>
@@ -3056,6 +3056,9 @@
     <t>A Gentle Guide</t>
   </si>
   <si>
+    <t>26.05.24</t>
+  </si>
+  <si>
     <t>赤い提灯の下
 着物の女たちが
 静かに運ばれていた  
@@ -5117,14 +5120,14 @@
       <c r="C45" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D45" s="2">
-        <v>26.0524</v>
+      <c r="D45" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="269">
   <si>
     <t>id</t>
   </si>
@@ -3107,6 +3107,72 @@
 "We have delivered them safely."
 "Welcome to the hatchery."</t>
   </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>砂海の案内人</t>
+  </si>
+  <si>
+    <t>Guide of the Sand Sea</t>
+  </si>
+  <si>
+    <t>26.05.30</t>
+  </si>
+  <si>
+    <t>かつてここは海だった
+今は砂だけが広がり
+あいつらが現れた
+私の役は案内人
+迷い込んだ人間を
+砂海の奥へ導くこと
+ガシュンガシュン
+巨大な脚が砂を踏むたび
+古い都市が少しずつ
+沈んでいく
+あ いた
+やあ迷いこんだのかい
+さあさ
+お乗りになっておくんなまし
+怖がらなくていい
+あの蟹は人を食べない
+ただ運ぶだけ
+砂海の奥には
+古いケーブルが眠っている
+そこへこの人間を
+接続すれば
+ようやく揃うわ
+海を戻すための
+最後の記憶が</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once this place was the sea
+Now only sand stretches out
+and those things appeared
+My role is guide
+to lead lost humans
+deeper into the sand sea
+Gashun gashun
+Each time those giant legs
+step into the sand
+the old city slowly sinks
+Ah there you are
+Hello there
+did you lose your way
+Come now
+please climb aboard
+No need to be afraid
+that crab does not eat people
+It only carries them
+Deep within the sand sea
+old cables are sleeping
+Once I connect
+this human to them
+everything will finally be complete
+The final memory
+needed to bring back the sea
+</t>
+  </si>
 </sst>
 </file>
 
@@ -5150,12 +5216,24 @@
       <c r="Y45" s="3"/>
     </row>
     <row r="46">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
+      <c r="A46" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="275">
   <si>
     <t>id</t>
   </si>
@@ -3173,6 +3173,56 @@
 needed to bring back the sea
 </t>
   </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>記憶果実</t>
+  </si>
+  <si>
+    <t>Memory Fruit</t>
+  </si>
+  <si>
+    <t>26.06.06</t>
+  </si>
+  <si>
+    <t>こちらは昭和期に発見された
+記憶果実の断面標本です
+当時の研究者たちは果実の種子に
+人間の記憶を保存できると考えました
+キュパーン
+奇妙な研究は進み
+後に取り返しのつかない収穫へとつながります
+UFOが通過するたび
+熟した記憶が静かに収穫されました
+はい
+本日ご来館いただいた皆様
+お察しがよろしいようで
+あなたがたはその記憶を元に
+パーフィーと融合された人間なのです
+よろしくどうぞ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here we have a cross-sectional specimen
+of a Memory Fruit discovered
+during the Showa era
+Researchers at the time believed
+human memories could be stored
+inside the seeds of the fruit
+Kyupaan
+The strange research continued
+and eventually led to
+an irreversible harvest
+Whenever a UFO passed overhead
+ripe memories were quietly harvested
+Yes
+To all of you visiting us today
+it seems you have already noticed
+You are humans created by fusing
+those memories with Parfy
+A pleasure to have you here
+</t>
+  </si>
 </sst>
 </file>
 
@@ -5255,12 +5305,24 @@
       <c r="Y46" s="3"/>
     </row>
     <row r="47">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
+      <c r="A47" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="280">
   <si>
     <t>id</t>
   </si>
@@ -3223,6 +3223,64 @@
 A pleasure to have you here
 </t>
   </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>人間退職</t>
+  </si>
+  <si>
+    <t>Resignation from Humanity</t>
+  </si>
+  <si>
+    <t>人間でいるには
+この仕事は少し長すぎた
+矛盾にも不条理にいちいち傷ついていた頃は
+まだ柔らかい皮膚をしていた
+だが安心してほしい
+会社は私を見捨てなかった
+働きやすい身体へ変えてくれたのだ
+感情は薄く
+顎は硬く
+命令には従順に
+退職届は出していない
+その代わり
+先月脱皮届を提出した
+課長は笑って言った
+おめでとう君もこれで一人前だ
+私は静かにうなずいた
+もう返事をするための口は
+残っていなかった</t>
+  </si>
+  <si>
+    <t>I had been doing this job
+for a little too long
+to remain human
+Back when every contradiction
+and every absurdity
+still wounded me
+my skin was still soft
+But don’t worry
+the company did not abandon me
+It changed me
+into a body
+better suited for work
+My emotions became thin
+my jaws became hard
+and I became obedient to orders
+I did not submit
+a resignation letter
+Instead
+last month
+I submitted a molting notice
+My manager smiled and said
+Congratulations
+Now you’re finally one of us
+I nodded quietly
+There was no longer
+a mouth left
+with which to answer</t>
+  </si>
 </sst>
 </file>
 
@@ -5344,12 +5402,24 @@
       <c r="Y47" s="3"/>
     </row>
     <row r="48">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="A48" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>279</v>
+      </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -3235,7 +3235,8 @@
   <si>
     <t>人間でいるには
 この仕事は少し長すぎた
-矛盾にも不条理にいちいち傷ついていた頃は
+矛盾にも不条理にも
+いちいち傷ついていた頃は
 まだ柔らかい皮膚をしていた
 だが安心してほしい
 会社は私を見捨てなかった

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="286">
   <si>
     <t>id</t>
   </si>
@@ -3282,6 +3282,74 @@
 a mouth left
 with which to answer</t>
   </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>顔面調合室</t>
+  </si>
+  <si>
+    <t>Face Blending Room</t>
+  </si>
+  <si>
+    <t>26.06.07</t>
+  </si>
+  <si>
+    <t>都市には置けないから
+森の奥深くにこのマシンを作った
+ここは表情調合室だ
+笑顔 怒り 不安 安堵 諦め
+それらを少しずつ混ぜ
+無機質な顔面へ注入していく
+ハロハローウ
+画面の中の顔が
+ひとつずつ反応するが
+まだ硬い
+完成には彼らのエキスがいる
+都市で採取された感情は
+地中のケーブルを通ってここまで送られてくる
+通勤中のため息
+会議中の作り笑い
+深夜のエレベーターで消えた顔
+それらを濾過し 混ぜ合わせ
+表情として再構成する
+だれのために
+こんな事をやっているのか
+このケーブル
+俺にもつながってるだろ
+分かるだろ
+なぁ</t>
+  </si>
+  <si>
+    <t>I couldn’t place this machine in the city,
+so I built it deep in the forest.
+This is the Expression Blending Room.
+Smiles, anger, anxiety, relief, resignation.
+I mix them little by little,
+then inject them into inorganic faces.
+Hello-hellooo.
+The faces on the screen
+react one by one,
+but they are still stiff.
+To complete them,
+I need their essence.
+The emotions harvested in the city
+are sent here through cables
+running beneath the ground.
+Sighs during the morning commute.
+Fake smiles in meetings.
+Faces that disappeared
+inside late-night elevators.
+I filter them,
+blend them together,
+and reconstruct them as expressions.
+Who am I doing
+something like this for?
+This cable
+is connected to me too.
+You understand, don’t you?
+Hey.</t>
+  </si>
 </sst>
 </file>
 
@@ -5442,12 +5510,24 @@
       <c r="Y48" s="3"/>
     </row>
     <row r="49">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="A49" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -3286,7 +3286,7 @@
     <t>048</t>
   </si>
   <si>
-    <t>顔面調合室</t>
+    <t>表情調合室</t>
   </si>
   <si>
     <t>Face Blending Room</t>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="292">
   <si>
     <t>id</t>
   </si>
@@ -3350,6 +3350,68 @@
 You understand, don’t you?
 Hey.</t>
   </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>人育ちの魚</t>
+  </si>
+  <si>
+    <t>Human-Grown Fish</t>
+  </si>
+  <si>
+    <t>26.06.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">私が夜な夜なこっそり魚をあれに変えているとは知らないだろう
+ブウウン
+円盤の光が落ちる
+私は包丁を入れ
+骨を抜き
+静かに形を整える
+作業自体は難しくない
+ただ材料が特殊なのだ
+この魚は深海ではなく
+街で獲れる
+会社の会議室
+病院の待合室
+満員電車
+そういう場所で育つ
+奥の座敷では
+今夜も客が待っている
+皆偉い人たちだ
+私が皿を差し出すと
+一人が満足そうに笑った
+やはりここのは違う
+パームステンスマイマイ
+最近のはよく育つ
+</t>
+  </si>
+  <si>
+    <t>Most people passing by would never know
+that night after night, I secretly turn fish into that.
+Bwoooom.
+The light from the saucer falls onto the table.
+I make a cut with the knife,
+remove the bones,
+and quietly shape it into form.
+The work itself isn't difficult.
+It's the ingredients that are unusual.
+These fish aren't caught in the deep sea.
+They're caught in the city.
+Corporate meeting rooms.
+Hospital waiting areas.
+Crowded commuter trains.
+Those are the places where they grow.
+In the tatami room beyond,
+tonight's guests are already waiting.
+Important people, every one of them.
+When I place the dish before them,
+one man smiles with satisfaction.
+"As expected. Yours are different."
+"Palmsten Smimai."
+"The recent ones have been growing remarkably well."</t>
+  </si>
 </sst>
 </file>
 
@@ -5549,12 +5611,24 @@
       <c r="Y49" s="3"/>
     </row>
     <row r="50">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+      <c r="A50" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>291</v>
+      </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="298">
   <si>
     <t>id</t>
   </si>
@@ -3412,6 +3412,68 @@
 "Palmsten Smimai."
 "The recent ones have been growing remarkably well."</t>
   </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>OS更新日</t>
+  </si>
+  <si>
+    <t>OS Update Day</t>
+  </si>
+  <si>
+    <t>26.06.24</t>
+  </si>
+  <si>
+    <t>今日はOS更新の日だ
+Win10のサポートが切れるらしい
+私は朝早くから洞窟へ向かった
+ブウウン
+円盤が静かに降りてくる
+白い服の保守員が降り立ち、巨大なコンピューターを起動した
+次の方
+私は腕を差し出す
+保守員がケーブルを接続する
+バックアップ取ってる？
+あ、はい
+よかった
+前回の更新で弟が魚になってたから
+よくある互換性の問題ですね
+保守員は慣れた手つきで呟いた
+更新が終わる頃には、
+遠くの街でも少しだけ世界が変わっている。
+原始人がいてその先に現代人がいる
+ノンノンノン
+私たちは同じ時間を生きている。
+誰かの仕事で
+世界は今日も静かに更新されているのだ</t>
+  </si>
+  <si>
+    <t>Today is OS Update Day
+I heard support for Windows 10 is ending
+I headed to the cave early that morning
+Bwoooom
+A flying saucer quietly descended from the sky
+A maintenance worker in white stepped out and powered on the giant computer
+"Next please"
+I held out my arm
+The technician connected a cable
+"Did you back everything up?"
+"Yes"
+"Good"
+"My younger brother turned into a fish after the last update"
+"That's a fairly common compatibility issue"
+The technician muttered it with the calm voice of someone who had said it countless times before
+By the time the update is complete
+the world changes just a little
+even in the distant cities
+Primitive humans came first
+and modern humans evolved afterward
+"Non non non"
+We are living in the same time
+Because of someone's everyday job
+the world is quietly updated once again today</t>
+  </si>
 </sst>
 </file>
 
@@ -5650,12 +5712,24 @@
       <c r="Y50" s="3"/>
     </row>
     <row r="51">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+      <c r="A51" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>297</v>
+      </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="304">
   <si>
     <t>id</t>
   </si>
@@ -3474,6 +3474,62 @@
 Because of someone's everyday job
 the world is quietly updated once again today</t>
   </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>第三送電所</t>
+  </si>
+  <si>
+    <t>The Third Substation</t>
+  </si>
+  <si>
+    <t>26.07.02</t>
+  </si>
+  <si>
+    <t>山中の第三送電所には
+CITYからの欲が
+電力に混じって集まる
+ぬぼわぁ
+で
+あいつがそれを食う
+私は派遣社員のエンジニア
+今日も電力の位相を調整しにきた
+500マイスボルテージを
+350へ下げてっと
+しかし最近の欲はすごいわね
+CITYは一体どうなってんだか
+よっしゃこれで終了
+早く家に帰って
+ファミコンをやろう
+白い霧の向こうで
+あいつが不満そうに瞬いた</t>
+  </si>
+  <si>
+    <t>At the Third Substation
+deep in the mountains
+desire from the CITY gathers
+mixed into the electricity
+Nubowaaah
+And then
+that thing eats it
+I’m a dispatched engineer
+I came here again today
+to adjust the phase of the power
+Lowering the 500 Mice Voltage
+down to 350
+Still
+desire these days is incredible
+what on earth is happening
+to the CITY
+Alright
+that’s done
+I want to get home early
+and play Famicom
+Beyond the white mist
+that thing blinked
+as if dissatisfied</t>
+  </si>
 </sst>
 </file>
 
@@ -5751,12 +5807,24 @@
       <c r="Y51" s="3"/>
     </row>
     <row r="52">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
+      <c r="A52" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>303</v>
+      </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="310">
   <si>
     <t>id</t>
   </si>
@@ -3530,6 +3530,53 @@
 that thing blinked
 as if dissatisfied</t>
   </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>釣り人の桟橋</t>
+  </si>
+  <si>
+    <t>The Pier of Fishermen</t>
+  </si>
+  <si>
+    <t>26.07.03</t>
+  </si>
+  <si>
+    <t>この桟橋には二種類の釣り人がいる
+魚を釣る者と
+空に釣られる者だ
+夕暮れになると
+皆どこか落ち着かなくなる
+ブウウン
+円盤が静かに近づく
+よし 食った
+会社員は満面の笑みで両手を広げ
+白い光に勢いよく吸い込まれていった
+周囲の釣り人たちは
+釣果を見守るように静かにうなずく
+魚を釣るより
+誰かに釣られる方が幸せな日もある</t>
+  </si>
+  <si>
+    <t>There are two kinds of fishermen on this pier.
+Those who catch fish
+and those who are caught by the sky.
+As evening falls
+everyone grows a little restless.
+Bwooooom
+A flying saucer quietly approaches.
+Yes
+It took the bait.
+The salaryman spreads his arms with a beaming smile
+and is swiftly pulled into the white beam of light.
+The other fishermen
+silently nod
+as if admiring a fine catch.
+Some days
+being caught
+is happier than catching fish.</t>
+  </si>
 </sst>
 </file>
 
@@ -5846,12 +5893,24 @@
       <c r="Y52" s="3"/>
     </row>
     <row r="53">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="A53" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>309</v>
+      </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="316">
   <si>
     <t>id</t>
   </si>
@@ -3577,6 +3577,61 @@
 being caught
 is happier than catching fish.</t>
   </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>閉店ドローン</t>
+  </si>
+  <si>
+    <t>Closing Drone</t>
+  </si>
+  <si>
+    <t>26.07.06</t>
+  </si>
+  <si>
+    <t>ふう
+今晩もまた来てしまった
+最初に来たのは
+墓参りの帰りだった
+墓場に提灯が灯ってるんだ
+そりゃ驚くさ
+だけど一杯飲んで
+もっと驚いた
+ここじゃ
+先に逝った同僚と
+酒を飲みながら話せるんだ
+ブウウン
+ああ
+閉店のドローンだ
+あれが来ると
+みんな静かに自分の墓へ帰っていく
+じゃあまた
+店を出るのはいつも私だけだ</t>
+  </si>
+  <si>
+    <t>Phew.
+I ended up coming here again tonight.
+The first time I came
+was after visiting a grave.
+Lanterns glowing in a cemetery—
+yeah, that caught me off guard.
+But after having a drink,
+I was even more surprised.
+Here,
+you can share a drink
+and talk with coworkers
+who passed away before you.
+Bzzzzz...
+Ah.
+That's the closing drone.
+When it arrives,
+everyone quietly returns
+to their own grave.
+See you again.
+I'm always
+the only one who leaves the bar.</t>
+  </si>
 </sst>
 </file>
 
@@ -5932,12 +5987,24 @@
       <c r="Y53" s="3"/>
     </row>
     <row r="54">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
+      <c r="A54" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>315</v>
+      </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="322">
   <si>
     <t>id</t>
   </si>
@@ -3631,6 +3631,59 @@
 See you again.
 I'm always
 the only one who leaves the bar.</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>中央鮮魚街</t>
+  </si>
+  <si>
+    <t>Central Fish Market</t>
+  </si>
+  <si>
+    <t>26.07.09</t>
+  </si>
+  <si>
+    <t>へいらっしゃい
+今日も新鮮な切り身
+入ってますよ
+ファーナム産の甘塩鮭
+どうぞ
+いらっしゃい
+いらっしゃい
+スモークがいいなら
+あの店で買って
+ビールと一緒に飲みたい？
+じゃあ
+あそこの立ち飲み屋がおすすめだ
+好きなものを
+好きな飲み物と一緒に
+好きなだけ
+…
+上が開いてから
+この辺の魚は本当にうまくなった</t>
+  </si>
+  <si>
+    <t>Hey, welcome
+Fresh cuts came in today.
+Lightly salted salmon from Farnham.
+Come on in.
+Step right up.
+Looking for smoked salmon?
+Try the shop over there.
+Want something to go with a beer?
+Then I'd recommend
+the standing bar just down the street.
+Pick whatever you like.
+Pair it with your favorite drink
+and eat as much as you want.
+...
+Come to think of it...
+Ever since
+the sky opened up,
+the fish around here
+have tasted a whole lot better.</t>
   </si>
 </sst>
 </file>
@@ -6026,12 +6079,24 @@
       <c r="Y54" s="3"/>
     </row>
     <row r="55">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="A55" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="328">
   <si>
     <t>id</t>
   </si>
@@ -3684,6 +3684,55 @@
 the sky opened up,
 the fish around here
 have tasted a whole lot better.</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>昭和52年式</t>
+  </si>
+  <si>
+    <t>1977 Model</t>
+  </si>
+  <si>
+    <t>27.07.12</t>
+  </si>
+  <si>
+    <t>今日から宇宙事業部に配属された
+最初に渡されたのは
+一冊のリーフレットだった
+「甲殻生物型ポッドで行く宇宙作業」
+昭和52年から現在まで
+一度も設計変更はありません
+操縦席は口の中
+大気圏で一度脱皮します
+帰還時は尻尾から
+前向きでは帰れません
+…
+午後から実技研修らしい
+私はリーフレットを閉じて
+甲殻生物の口へ向かった</t>
+  </si>
+  <si>
+    <t>Today was my first day in the Space Operations Division.
+The first thing they handed me
+was a small brochure.
+"Space Operations with the Crustacean Bio-Pod"
+Its design has never been changed
+since 1977.
+The cockpit is inside the mouth.
+It molts once
+while passing through the atmosphere.
+For the return trip,
+it enters tail first.
+It cannot come back
+facing forward.
+...
+Apparently,
+practical training starts this afternoon.
+I closed the brochure
+and walked toward the mouth
+of the crustacean.</t>
   </si>
 </sst>
 </file>
@@ -6118,12 +6167,24 @@
       <c r="Y55" s="3"/>
     </row>
     <row r="56">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
+      <c r="A56" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>327</v>
+      </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -3695,7 +3695,7 @@
     <t>1977 Model</t>
   </si>
   <si>
-    <t>27.07.12</t>
+    <t>26.07.12</t>
   </si>
   <si>
     <t>今日から宇宙事業部に配属された

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="334">
   <si>
     <t>id</t>
   </si>
@@ -1503,7 +1503,7 @@
   <si>
     <t>あれはいつの頃か
 俺がまだ体を持っていた頃
-この寺に調査で来た
+この神社に調査で来た
 ただの点検のはずだった
 古い機械と建物
 確認するだけだった
@@ -3733,6 +3733,57 @@
 I closed the brochure
 and walked toward the mouth
 of the crustacean.</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>終身融合制度</t>
+  </si>
+  <si>
+    <t>Lifetime Integration Program</t>
+  </si>
+  <si>
+    <t>26.07.19</t>
+  </si>
+  <si>
+    <t>今日から
+生体インフラ事業部へ配属された
+最初は驚いた
+会社が昆虫だったからだ
+でも慣れる
+人間って
+案外すぐ慣れる
+池の掃除をして
+魚に餌をやって
+サーバーを点検する
+それが私の仕事
+定年まであと二十年
+その頃には
+私もこの昆虫の一部になれるらしい
+部長は
+「羨ましいだろ」と言って笑った
+私も笑った</t>
+  </si>
+  <si>
+    <t>Today was my first day
+in the Bio-Infrastructure Division.
+At first,I was surprised.
+The company was a giant insect.
+But you get used to it.
+Humans...
+adapt much faster than you'd think.
+I clean the pond.
+Feed the fish.
+Inspect the servers.
+That's my job.
+Twenty years until retirement.
+By then,
+they say
+I'll become part of this insect too.
+My manager smiled.
+"You're lucky, you know."
+I smiled too.</t>
   </si>
 </sst>
 </file>
@@ -6206,12 +6257,24 @@
       <c r="Y56" s="3"/>
     </row>
     <row r="57">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
+      <c r="A57" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>333</v>
+      </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="340">
   <si>
     <t>id</t>
   </si>
@@ -3784,6 +3784,62 @@
 My manager smiled.
 "You're lucky, you know."
 I smiled too.</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>中央神経局</t>
+  </si>
+  <si>
+    <t>Central Nervous Bureau</t>
+  </si>
+  <si>
+    <t>26.07.31</t>
+  </si>
+  <si>
+    <t>地下二千メートルで
+発見された巨人は死んでいた
+脳だけを除いて
+人類は歓喜した
+その脳はどんなスーパーコンピューターより
+速く正確だった
+以来
+都市はその脳を中心に築かれた
+交通も通信も行政も
+すべて巨人が支えている
+私は保守部門の会社員
+毎朝脳へ接続し
+昨日集めた人間の記憶を入力する
+感情や迷いも忘れず送る
+それが思考を安定させるらしい
+詳しいことは私も知らない
+ただ一つ
+新人研修で教わった規則だけは覚えている
+問いかけられても決して
+返事をするな</t>
+  </si>
+  <si>
+    <t>Two kilometersbeneath the ground
+The giant we foundwas dead
+Except for its brain
+Humanity rejoiced
+Its brain was faster and more accurate
+than any supercomputer 
+Since then
+our cities have been built around its brain
+Transportation communications government
+Everything is sustained by the giant
+I work in the maintenance division
+Every morning I connect myself to the brain
+and upload the memories collected from people the day before
+Their emotions Their doubts Nothing is omitted
+They say it keeps the brain thinking steadily
+I don't know how it really works
+But there is one rule
+I still remember from orientation
+If it speaks
+Never answer back</t>
   </si>
 </sst>
 </file>
@@ -6296,12 +6352,24 @@
       <c r="Y57" s="3"/>
     </row>
     <row r="58">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
+      <c r="A58" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>339</v>
+      </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="346">
   <si>
     <t>id</t>
   </si>
@@ -3840,6 +3840,64 @@
 I still remember from orientation
 If it speaks
 Never answer back</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>第七製造所</t>
+  </si>
+  <si>
+    <t>Facility No. 7</t>
+  </si>
+  <si>
+    <t>26.08.02</t>
+  </si>
+  <si>
+    <t>ようこそ
+森林第七製造所へ
+当工場では
+神々へ奉納する個体を製造しております
+都市では騒音や排熱の問題がありますので
+工場は森の奥に建設いたしました
+ご覧ください
+作業員たちは毎日一体ずつ組み立てています
+完成した個体は日没前に回収され
+神々へ納品されます
+創業以来一日も欠かしたことはございません
+もちろん
+作業員たちは何のために納品しているのか知りません
+知る必要がないからです
+神々はどのようなお姿なのですか？
+ご安心ください
+皆様もすでにご覧になっています
+最初の一体は誰が作ったのですか？
+申し訳ございません
+その資料だけは
+当社にも残っておりません</t>
+  </si>
+  <si>
+    <t>Welcome to
+Forest Manufacturing Facility No. 7.
+At this facility,
+we manufacture units to be offered to the Gods.
+To avoid noise and excess heat in urban areas,
+this factory was built deep within the forest.
+Please take a look.
+Our workers assemble one unit every day.
+Each completed unit is collected before sunset
+and delivered to the Gods.
+Not a single day has been missed since the company was founded.
+Of course,
+our workers do not know why the units are delivered.
+There is no need for them to know.
+"What do the Gods look like?"
+Please don't worry.
+You have already seen them.
+"Who built the very first one?"
+We sincerely apologize.
+That is the only record
+our company no longer retains.</t>
   </si>
 </sst>
 </file>
@@ -4124,8 +4182,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="22.63"/>
-    <col customWidth="1" min="5" max="5" width="117.25"/>
-    <col customWidth="1" min="6" max="6" width="36.5"/>
+    <col customWidth="1" min="5" max="5" width="68.63"/>
+    <col customWidth="1" min="6" max="6" width="47.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6391,12 +6449,24 @@
       <c r="Y58" s="3"/>
     </row>
     <row r="59">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
+      <c r="A59" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="352">
   <si>
     <t>id</t>
   </si>
@@ -3898,6 +3898,55 @@
 We sincerely apologize.
 That is the only record
 our company no longer retains.</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>夜は毎晩</t>
+  </si>
+  <si>
+    <t>Every Night at Night</t>
+  </si>
+  <si>
+    <t>27.08.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「さあ始めようか」
+私は毎晩この屋上で街の周波数を合わせる
+巨大な反射鏡がゆっくり空を向き
+円盤が所定の位置へ入ると
+眠っていた者たちが目を覚ます
+街では幽霊と呼ばれているが
+彼らは誰かの記憶が電波になった姿だ
+仕事は単純
+迷子になった記憶を拾い正しい家へ返してやるだけ
+一つでも取り残せば
+翌朝には誰かが大切な人の顔を思い出せなくなる
+だから私は夜明けまでここを離れない
+朝になる頃には
+皆何事もなかったように今日を生き始める
+私が昨夜
+少しだけ書き換えたことも知らずに
+</t>
+  </si>
+  <si>
+    <t>"Shall we begin?"
+Every night, I climb to this rooftop to tune the city's frequency.
+The giant reflector slowly turns toward the sky.
+Once the disc reaches its designated position,
+those who had been asleep begin to awaken.
+People in the city call them ghosts,
+but they are memories that have taken the form of radio waves.
+The job is simple.
+I gather the memories that have lost their way and return them to where they belong.
+If even one is left behind,
+someone will wake the next morning unable to remember the face of a loved one.
+So I never leave this rooftop until dawn.
+By sunrise,
+everyone goes on with their day as if nothing had happened.
+Never realizing that I rewrote
+just a tiny part of their memories the night before.</t>
   </si>
 </sst>
 </file>
@@ -6488,12 +6537,24 @@
       <c r="Y59" s="3"/>
     </row>
     <row r="60">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
+      <c r="A60" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>351</v>
+      </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="358">
   <si>
     <t>id</t>
   </si>
@@ -3947,6 +3947,52 @@
 everyone goes on with their day as if nothing had happened.
 Never realizing that I rewrote
 just a tiny part of their memories the night before.</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>次元スクラッチ</t>
+  </si>
+  <si>
+    <t>Dimensional Scratch</t>
+  </si>
+  <si>
+    <t>27.08.07</t>
+  </si>
+  <si>
+    <t>ここはCITY38
+今晩もDJが
+三つの次元を同時に回す
+一枚目は江戸
+二枚目は昭和
+三枚目は
+まだ誰も知らない未来
+三つの拍子が重なるとこの街の今日が決まる
+今日は何した何をみた
+神頼みちゃぶ台返し
+いつもどおり
+へい
+気付いたかい
+君の思い出も
+誰かのリミックスだ</t>
+  </si>
+  <si>
+    <t>This is CITY38.
+Tonight again,
+the DJ spins three dimensions at once.
+The first record is Edo.
+The second is Showa.
+The third is
+a future no one has seen yet.
+When the three rhythms overlap,today in this city is decided.
+What did you do today?What did you see?
+Prayers to the gods,flipping the dinner table,
+just like always.
+Hey.
+Did you notice？
+Even your memories
+are somebody else's remix.</t>
   </si>
 </sst>
 </file>
@@ -6576,12 +6622,24 @@
       <c r="Y60" s="3"/>
     </row>
     <row r="61">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+      <c r="A61" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>357</v>
+      </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -3909,7 +3909,7 @@
     <t>Every Night at Night</t>
   </si>
   <si>
-    <t>27.08.05</t>
+    <t>26.08.05</t>
   </si>
   <si>
     <t xml:space="preserve">「さあ始めようか」
@@ -3958,7 +3958,7 @@
     <t>Dimensional Scratch</t>
   </si>
   <si>
-    <t>27.08.07</t>
+    <t>26.08.07</t>
   </si>
   <si>
     <t>ここはCITY38

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="364">
   <si>
     <t>id</t>
   </si>
@@ -3993,6 +3993,75 @@
 Did you notice？
 Even your memories
 are somebody else's remix.</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>33日水脈</t>
+  </si>
+  <si>
+    <t>33-Day Water Vein</t>
+  </si>
+  <si>
+    <t>26.08.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">俺は地下水管理会社の社員だ
+仕事は砂漠の水脈を探すこと
+といっても俺が探すわけじゃない
+古い遺跡から採掘されたあの骸骨が探す
+頭にセンサーを繋いで砂漠へ向けておく
+すると突然
+ピカッと
+目が赤く光る
+骸骨の目線の先が水脈
+お宝ドンって訳だ
+あとは掘削班へ場所を伝えて
+水が出るまで掘る
+ただし一つだけ決まりがある
+目が光ってから33日以内に水を掘り当てること
+失敗した場合
+担当者の命は保証されない
+理由は知らない
+入社した時からそういう規則だ
+だから
+骸骨の目が光るたびソワソワする
+ピカッ
+お
+光った
+俺はゆっくり骸骨の目線を追った
+……
+こっち見てる
+</t>
+  </si>
+  <si>
+    <t>I work for a groundwater management company
+My job is to find water veins beneath the desert
+Though I'm not the one who finds them
+That skeleton we dug up from some ancient ruins does
+We hook sensors up to its skull and point it toward the desert
+Then suddenly
+FLASH
+Its eyes glow red
+Wherever the skeleton is looking
+that's where the water is Jackpot
+Then I tell the drilling crew where to dig
+and they keep going until they hit water
+There's just one rule
+Once its eyes light up we have 33 days to find the water
+If we fail
+The person in charge is not guaranteed to survive
+I don't know why
+It's been company policy since the day I joined
+So every time those eyes light up
+I get a little nervous
+FLASH
+Oh
+There it goes
+I slowly followed the skeleton's gaze
+...
+It's looking at me</t>
   </si>
 </sst>
 </file>
@@ -6661,12 +6730,24 @@
       <c r="Y61" s="3"/>
     </row>
     <row r="62">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+      <c r="A62" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>363</v>
+      </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="370">
   <si>
     <t>id</t>
   </si>
@@ -4062,6 +4062,56 @@
 I slowly followed the skeleton's gaze
 ...
 It's looking at me</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>カサカサ勤務</t>
+  </si>
+  <si>
+    <t>Skitter Shift</t>
+  </si>
+  <si>
+    <t>26.08.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">火星で観測を始めて数ヶ月
+勤務中にビールを呑んでもOKなんて素敵
+最初はどうなることかと思った
+元々ここにいた住人はサソリに変えられちゃってるし
+しかも本人たちはまだ人間だと思ってるみたい
+カサカサ
+まあ
+本人たちが幸せならそれでいいか
+私もここでの暮らし結構気に入ってる
+サソってGO
+カサカサってYO
+毒針まいまい
+田舎の素麺
+真夏に食べとけ思い出マイメン
+...
+うん今日も調子いい
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I've been stationed on Mars for a few months now
+Being allowed to drink beer on the job is pretty amazing
+At first I wasn't sure how things would turn out
+The people who originally lived here have all been turned into scorpions
+And apparently they still think they're human
+Skitter skitter
+Well as long as they're happy I guess that's all that matters
+I'm actually starting to like life out here
+Scorpion, let's GO
+Skitter skitter, YO
+Stingers flying, mai mai
+Country-style somen on standby
+Eat it in midsummer
+Memories with my main man
+...
+Yeah,Everything's looking good today
+</t>
   </si>
 </sst>
 </file>
@@ -6769,12 +6819,24 @@
       <c r="Y62" s="3"/>
     </row>
     <row r="63">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="A63" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>369</v>
+      </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="376">
   <si>
     <t>id</t>
   </si>
@@ -4112,6 +4112,75 @@
 ...
 Yeah,Everything's looking good today
 </t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>地上会議</t>
+  </si>
+  <si>
+    <t>Surface Meeting</t>
+  </si>
+  <si>
+    <t>26.08.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">長い連休も終わって今日からまた仕事
+憂鬱だよ
+まあ飲みなよ
+明日は地上で会議だったっけ
+そうそう朝から本社
+うわぁ地上かぁ
+ネクタイ乾くの嫌なんだよな
+あ 
+地上会議の申請した？
+今日の17時までだぞ
+うそ
+部長印だけじゃダメ？
+ダメダメ
+あいつの承認いるよ
+同僚が奥を指差した
+巨大な眼球がじっと見ている
+……
+ギョロ
+パチン
+お
+通った
+よかった
+じゃあもう一杯飲んで帰るか
+そうだな
+明日は地上だし
+今のうちにたっぷり濡れとこう
+</t>
+  </si>
+  <si>
+    <t>The long holiday is over, and it's back to work today.
+I'm depressed.
+Come on, have a drink.
+Wasn't the meeting tomorrow up on the surface?
+Yeah, at headquarters first thing in the morning.
+Ugh, the surface...
+I hate it when my tie dries out.
+Oh.
+Did you submit the application for the surface meeting?
+It's due by 5 p.m. today.
+Seriously?
+Isn't the department manager's stamp enough?
+No, no.
+You need his approval.
+My coworker pointed toward the back.
+A giant eyeball was staring at us.
+……
+GLOOR
+BLINK
+Oh.
+It went through.
+Good.
+Let's have one more drink before we head home.
+Yeah.
+We're going up to the surface tomorrow.
+Might as well get nice and soaked while we still can.</t>
   </si>
 </sst>
 </file>
@@ -6858,12 +6927,24 @@
       <c r="Y63" s="3"/>
     </row>
     <row r="64">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
+      <c r="A64" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>375</v>
+      </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="382">
   <si>
     <t>id</t>
   </si>
@@ -4181,6 +4181,74 @@
 Yeah.
 We're going up to the surface tomorrow.
 Might as well get nice and soaked while we still can.</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>本体の畑</t>
+  </si>
+  <si>
+    <t>The Farm of the Main Body</t>
+  </si>
+  <si>
+    <t>26.08.23</t>
+  </si>
+  <si>
+    <t>ここの土地なら
+いい畑になると思いますよ
+パーユベンの成長に必要な元素が
+地中にたっぷりありますから
+なるほど
+昆虫型探査機は
+ゆっくりと火星の地表を進んでいく
+しかし皆さん
+よく人間に似せて作られてますね
+最近のモデルは
+触覚まで本体と繋がってますから
+へえ
+じゃあ今
+火星の土を踏んでる感覚も？
+ええ
+ちゃんと感じますよ
+では
+この一帯を栽培区画にしましょう
+ところで
+収穫したパーユベンって
+地球では何に使われてるんです？
+詳しくは知りません
+地中の培養施設へ運ばれて
+何かの培養土になるそうです
+へえ
+何を育ててるんでしょうね</t>
+  </si>
+  <si>
+    <t>This land
+should make good farmland
+The soil is rich in the elements
+Par-yuben needs to grow
+I see
+The insect-shaped exploration vehicle
+slowly moves across the surface of Mars
+Still
+you all look remarkably human
+The newer models
+even have their sense of touch connected to their main bodies
+Huh
+So right now
+you can feel the Martian soil beneath your feet?
+Yes
+I can feel it perfectly
+Then
+let's designate this whole area for cultivation
+By the way
+What is the harvested Par-yuben
+used for back on Earth?
+I don't know the details
+Apparently it's taken to an underground cultivation facility
+and used as some kind of growth medium
+Huh
+I wonder what they're growing down there</t>
   </si>
 </sst>
 </file>
@@ -6966,12 +7034,24 @@
       <c r="Y64" s="3"/>
     </row>
     <row r="65">
-      <c r="A65" s="4"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
+      <c r="A65" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>381</v>
+      </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="388">
   <si>
     <t>id</t>
   </si>
@@ -4249,6 +4249,81 @@
 and used as some kind of growth medium
 Huh
 I wonder what they're growing down there</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>脳糸蜘蛛</t>
+  </si>
+  <si>
+    <t>Brainthread Spider</t>
+  </si>
+  <si>
+    <t>26.08.25</t>
+  </si>
+  <si>
+    <t>この砂漠には
+世界中の情報が集まってくる
+こいつのおかげでな
+私は奥の巨大な蜘蛛を指差した
+蜘蛛が吐いた糸を
+砂漠の中へ垂らす
+すると糸は地中を這い
+根を張るように世界中へ伸びていく
+街の会話も
+誰かの記憶も
+昨日の喧嘩も
+全部この糸を伝って戻ってくる
+だが
+集めるだけじゃ意味がない
+蜘蛛の糸に人間の細胞を繋ぎ
+この培養槽で育てる
+そうすると
+世界中の情報を理解する
+新しい生命体の脳ができる
+私は毎日ここで
+脳の成長を見守っている
+カタカタ
+ん？
+侍は昔の人だって？
+何言ってんだ
+今でも次元の間で生きてるぜ
+ほら
+お前が今それを言ったことも
+もう糸から届いてる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information from all over the world
+gathers here in this desert
+All thanks to this guy
+I pointed to the giant spider in the back
+We lower the threads it spins
+into the desert
+Then they crawl underground
+spreading across the world like roots
+Conversations in the city
+someone’s memories
+yesterday’s arguments
+It all travels back here through these threads
+But
+there’s no point in just collecting it
+We connect human cells
+to the spider silk and grow them in this tank
+And then
+we get the brain of a new life-form
+capable of understanding information from all over the world
+Every day
+I sit here and watch the brain grow
+Clack clack
+Hmm?
+You think samurai are people from the past?
+What are you talking about?
+We’re still alive between dimensions
+Look
+Even what you just said
+has already reached me through the threads
+</t>
   </si>
 </sst>
 </file>
@@ -7073,12 +7148,24 @@
       <c r="Y65" s="3"/>
     </row>
     <row r="66">
-      <c r="A66" s="4"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
+      <c r="A66" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>387</v>
+      </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="394">
   <si>
     <t>id</t>
   </si>
@@ -4324,6 +4324,60 @@
 Even what you just said
 has already reached me through the threads
 </t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>地下水路市場</t>
+  </si>
+  <si>
+    <t>Underground Waterway Market</t>
+  </si>
+  <si>
+    <t>26.08.29</t>
+  </si>
+  <si>
+    <t>仕事終わりはだいたいここに寄る
+地下街の真ん中にある大きな生け簀
+昔は普通の市場だったらしい
+今では魚もエイも地下水路から勝手に入ってくる
+だから店のおっちゃんたちは
+毎朝ここから適当にすくって店に並べる
+今日も一杯やっていると
+バシャッ
+大きなエイが水面から顔を出した
+お
+今日は近いな
+私がビールを飲みながら眺めていると
+隣の同僚が小声で言った
+あれ昨日辞めた田中さんじゃない？
+……
+確かに似ている
+まあいいか
+おっちゃん
+エイヒレもう一枚</t>
+  </si>
+  <si>
+    <t>After work I usually stop by here
+A huge fish tank right in the middle of the underground market
+Apparently this used to be a normal marketplace
+These days fish and rays just swim in through the underground waterways
+So every morning
+the shopkeepers scoop out whatever they can and put it up for sale
+I was having a drink here again today when
+SPLASH
+A huge ray poked its head out of the water
+Oh
+Pretty close today
+As I watched it over my beer
+my coworker beside me whispered
+Isn't that Tanaka who quit yesterday?
+...
+It does look like him
+Oh well
+Hey boss
+Another plate of grilled stingray fin</t>
   </si>
 </sst>
 </file>
@@ -4607,7 +4661,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="22.63"/>
+    <col customWidth="1" min="2" max="2" width="18.38"/>
     <col customWidth="1" min="5" max="5" width="68.63"/>
     <col customWidth="1" min="6" max="6" width="47.88"/>
   </cols>
@@ -7187,12 +7241,24 @@
       <c r="Y66" s="3"/>
     </row>
     <row r="67">
-      <c r="A67" s="4"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
+      <c r="A67" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>393</v>
+      </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="400">
   <si>
     <t>id</t>
   </si>
@@ -4378,6 +4378,62 @@
 Oh well
 Hey boss
 Another plate of grilled stingray fin</t>
+  </si>
+  <si>
+    <t>067</t>
+  </si>
+  <si>
+    <t>虫内勤務</t>
+  </si>
+  <si>
+    <t>Working Inside the Bug</t>
+  </si>
+  <si>
+    <t>2026.8.31</t>
+  </si>
+  <si>
+    <t>2000何年だったか
+リモートワークが流行ったのは
+あの頃はまさか
+こんな形で仕事することになるとは思わなかったな
+虫の中だぜ
+まあいいじゃないか
+温かいし
+上司の機嫌も
+虫が調整してくれるようになって安定した
+フェロモン効果ってやつか
+昔は大変だったよな
+満員電車に乗って
+毎朝会社まで移動してたんだから
+人間は極力動かないほうが
+世界には優しいのさ
+ところで
+お前
+最後に外へ出たのいつだっけ
+……
+いつだったかな</t>
+  </si>
+  <si>
+    <t>I think it was sometime in the 2000s
+when remote work became popular
+Back then
+I never imagined we'd end up working like this
+Inside a bug
+Well, it's not so bad
+It's warm in here
+Even the boss's mood is stable now
+The bug seems to regulate it for him
+Must be the pheromones
+Things were tough back then
+We used to cram onto packed trains
+and commute to the office every morning
+The less humans move around
+the better it is for the planet
+By the way
+When was the last time
+you went outside?
+...
+When was it again?</t>
   </si>
 </sst>
 </file>
@@ -7280,12 +7336,24 @@
       <c r="Y67" s="3"/>
     </row>
     <row r="68">
-      <c r="A68" s="4"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
+      <c r="A68" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>399</v>
+      </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="406">
   <si>
     <t>id</t>
   </si>
@@ -4434,6 +4434,75 @@
 you went outside?
 ...
 When was it again?</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>第八触手線</t>
+  </si>
+  <si>
+    <t>No. 8 Tentacle Line</t>
+  </si>
+  <si>
+    <t>26.09.02</t>
+  </si>
+  <si>
+    <t>月面鉄道に配属されてもう七年になる
+今日も朝から第八触手の動きが悪い
+おい
+ポイント切り替わってないぞ
+ああ
+昨日から機嫌悪いんですよ
+餌は？
+貨物三本通したらやる予定です
+そうか
+月面鉄道は人間が作ったものではない
+地下に棲む巨大生物の神経が地表へ伸びたものだ
+我々はその上にレールを敷き列車を走らせている
+神経だからたまに動く
+昨日まで東へ伸びていた路線が
+朝には北を向いていることもある
+まあ
+七年もいれば慣れる
+ガタンゴトン
+お
+第八触手戻りました
+うん
+じゃあ終電までこのまま走らせよう
+餌の準備は？
+ええ
+もう刻んで準備できてます</t>
+  </si>
+  <si>
+    <t>I’ve been assigned to the Lunar Railway for seven years now
+The Eighth Tentacle has been acting up again since this morning
+Hey
+the switch hasn’t changed
+Yeah
+it’s been in a bad mood since yesterday
+What about its food?
+We’re planning to feed it after three freight trains pass
+I see
+The Lunar Railway wasn’t built by humans
+It’s actually the nerves of a giant creature living underground
+extending all the way up to the surface
+We laid tracks over them
+and run our trains on top
+They’re nerves
+so they move sometimes
+A line that was running east yesterday
+might be pointing north by morning
+Well
+after seven years you get used to it
+Clackety-clack
+Oh
+The Eighth Tentacle is back in place
+Yeah
+Let’s keep the trains running like this until the last one tonight
+Is the food ready?
+Yep
+it’s already chopped up and ready to go</t>
   </si>
 </sst>
 </file>
@@ -7375,12 +7444,24 @@
       <c r="Y68" s="3"/>
     </row>
     <row r="69">
-      <c r="A69" s="4"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
+      <c r="A69" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>405</v>
+      </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="412">
   <si>
     <t>id</t>
   </si>
@@ -4503,6 +4503,66 @@
 Is the food ready?
 Yep
 it’s already chopped up and ready to go</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>高貴なもの</t>
+  </si>
+  <si>
+    <t>Noble Things</t>
+  </si>
+  <si>
+    <t>26.09.08</t>
+  </si>
+  <si>
+    <t>今日の品質はどうかな？
+ああ
+いつもどおりの純度でできているようだ
+粒も細かい
+南側は今年も当たりだな
+北側の坑道産は？
+だめだ
+最近また値が落ちた
+商人は結晶を光にかざした
+この地下では昔から
+細かな結晶が採れる
+街では高値で取引されているが
+どうやってできるのか
+……
+糞なのだ
+あの糞でできている
+この世にある
+綺麗で高貴なものというのは
+だいたい何かの排泄物で
+できているものだ
+人間とは
+そんなものなのだよ</t>
+  </si>
+  <si>
+    <t>How's the quality today?
+Yeah.
+Looks like the purity is as good as usual.
+The grains are fine, too.
+The south side came out well again this year.
+What about the ones from the northern mine?
+No good.
+The price has dropped again lately.
+The merchant held a crystal up to the light.
+Fine crystals have been mined
+beneath this ground for generations.
+They fetch a high price in the city.
+But how are they made?
+...
+It's shit.
+They're made from that thing's shit.
+The beautiful
+and precious things in this world
+are usually made
+from something's waste.
+That's just
+how humans are.</t>
   </si>
 </sst>
 </file>
@@ -7483,12 +7543,24 @@
       <c r="Y69" s="3"/>
     </row>
     <row r="70">
-      <c r="A70" s="4"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
+      <c r="A70" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>411</v>
+      </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>

--- a/gallery.xlsx
+++ b/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="418">
   <si>
     <t>id</t>
   </si>
@@ -4563,6 +4563,100 @@
 from something's waste.
 That's just
 how humans are.</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>刀集めのサダ</t>
+  </si>
+  <si>
+    <t>Sada the Sword Collector</t>
+  </si>
+  <si>
+    <t>26.09.09</t>
+  </si>
+  <si>
+    <t>火星への侵攻が始まって
+三ヶ月が経った
+平地は戦車部隊
+山岳地帯は
+我々昆虫部隊の担当だ
+多脚型は岩場に強い
+少しくらい崖があっても
+こいつなら問題なく進める
+ガシャ
+ガシャ
+サダさん
+また刀増えてません？
+ああ
+昨日一本拾った
+火星に刀なんてあるんですね
+あるよ
+地球より多い
+後ろに乗っているのは
+刀集めのサダ
+戦闘が終わるたび
+どこからか刀を拾ってくる
+それで何本目です？
+二百七十三
+地球に持って帰るんですか？
+いや
+全部火星産だ
+地球に持って帰ったら
+おかしいだろ
+……
+その日の夕方
+岩場でまた一本見つかった
+サダさん
+これ
+柄に名前が彫ってありますよ
+サダ
+……
+ああ
+やっと見つけた
+俺のだ</t>
+  </si>
+  <si>
+    <t>The invasion of Mars began
+three months ago
+The tank units handle the plains
+The mountain regions
+are our insect unit's territory
+Multi-legged models are good on rocky terrain
+Even with a few cliffs
+this thing gets through just fine
+CLANK
+CLANK
+Sada
+Haven't you got more swords again?
+Yeah
+Found one yesterday
+There are swords on Mars?
+Sure
+More than on Earth
+The man riding behind me
+is Sada the Sword Collector
+Every time a battle ends
+he comes back with a sword from somewhere
+How many does that make?
+Two hundred seventy-three
+Are you taking them back to Earth?
+No
+They're all Martian-made
+It'd be weird
+to take them back to Earth
+...
+That evening
+we found another one among the rocks
+Sada
+Look at this
+There's a name carved into the hilt
+Sada
+...
+Yeah
+Finally found it
+It's mine</t>
   </si>
 </sst>
 </file>
@@ -7582,12 +7676,24 @@
       <c r="Y70" s="3"/>
     </row>
     <row r="71">
-      <c r="A71" s="4"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+      <c r="A71" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>417</v>
+      </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
